--- a/VerveStacks_MYS_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_MYS_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_MYS_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3991046A-76AF-4900-B649-4448DE0B3646}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D1082310-C008-4282-BDB5-7C44B7D81792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -826,16 +826,70 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_MYS_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MYS_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MYS_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_MYS_012</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 12</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
+    <t>distr_solelc_spv_MYS_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MYS_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MYS_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MYS_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MYS_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MYS_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
   </si>
   <si>
     <t>distr_solelc_spv_MYS_003</t>
@@ -844,46 +898,16 @@
     <t>connecting solar to buses in cluster 3</t>
   </si>
   <si>
-    <t>distr_solelc_spv_MYS_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MYS_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MYS_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MYS_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MYS_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MYS_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MYS_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
+    <t>distr_solelc_spv_MYS_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MYS_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
   </si>
   <si>
     <t>distr_solelc_spv_MYS_001</t>
@@ -892,10 +916,10 @@
     <t>connecting solar to buses in cluster 1</t>
   </si>
   <si>
-    <t>distr_solelc_spv_MYS_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
+    <t>distr_solelc_spv_MYS_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
   </si>
   <si>
     <t>distr_solelc_spv_MYS_008</t>
@@ -910,42 +934,33 @@
     <t>connecting solar to buses in cluster 14</t>
   </si>
   <si>
-    <t>distr_solelc_spv_MYS_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MYS_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MYS_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MYS_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_w691239971-275_MYS,e_w325835238-275_MYS,e_MY68-275_MYS,e_w561806959-275_MYS,e_w399307646-275_MYS,e_w320246940-275_MYS</t>
+  </si>
+  <si>
+    <t>e_w399307647-275_MYS,e_w1137665609-275_MYS,e_w691633793-275_MYS,e_w691633796-275_MYS,e_w513610290-275_MYS</t>
+  </si>
+  <si>
+    <t>e_MY68-275_MYS,e_w561806959-275_MYS,e_w934653890-275_MYS</t>
+  </si>
+  <si>
     <t>e_w1137665620-500_MYS,e_w513950834-275_MYS,e_w1285211558-275_MYS,e_MY16-275_MYS</t>
   </si>
   <si>
+    <t>e_MY59-275_MYS</t>
+  </si>
+  <si>
     <t>e_w450080688-275_MYS,e_w328415531-275_MYS</t>
   </si>
   <si>
+    <t>e_MY25-500_MYS,e_w1137665617-275_MYS,e_w1137665620-500_MYS,e_w513950834-275_MYS</t>
+  </si>
+  <si>
     <t>e_w691200886-275_MYS,e_w235943019-275_MYS,e_w235951698-275_MYS</t>
   </si>
   <si>
@@ -955,31 +970,22 @@
     <t>e_MY16-275_MYS,e_MY12-275_MYS,e_w328415531-275_MYS</t>
   </si>
   <si>
-    <t>e_MY68-275_MYS,e_w561806959-275_MYS,e_w934653890-275_MYS</t>
-  </si>
-  <si>
-    <t>e_w691239971-275_MYS,e_w325835238-275_MYS,e_MY68-275_MYS,e_w561806959-275_MYS,e_w399307646-275_MYS,e_w320246940-275_MYS</t>
-  </si>
-  <si>
-    <t>e_w399307647-275_MYS,e_w1137665609-275_MYS,e_w691633793-275_MYS,e_w691633796-275_MYS,e_w513610290-275_MYS</t>
-  </si>
-  <si>
-    <t>e_MY25-500_MYS,e_w1137665617-275_MYS,e_w1137665620-500_MYS,e_w513950834-275_MYS</t>
+    <t>e_w236051516-275_MYS,e_w513610290-275_MYS,e_w1137665615-275_MYS,e_MY59-275_MYS,e_w1137665620-500_MYS</t>
+  </si>
+  <si>
+    <t>e_w320246940-275_MYS,e_w934653890-275_MYS,e_w513610290-275_MYS</t>
   </si>
   <si>
     <t>e_w328415531-275_MYS</t>
   </si>
   <si>
-    <t>e_w320246940-275_MYS,e_w934653890-275_MYS,e_w513610290-275_MYS</t>
-  </si>
-  <si>
     <t>e_w561806959-275_MYS,e_w235966081-275_MYS</t>
   </si>
   <si>
-    <t>e_MY59-275_MYS</t>
-  </si>
-  <si>
-    <t>e_w236051516-275_MYS,e_w513610290-275_MYS,e_w1137665615-275_MYS,e_MY59-275_MYS,e_w1137665620-500_MYS</t>
+    <t>distr_wonelc_won_MYS_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
   </si>
   <si>
     <t>distr_wonelc_won_MYS_001</t>
@@ -1000,12 +1006,6 @@
     <t>connecting wind onshore to buses in cluster 6</t>
   </si>
   <si>
-    <t>distr_wonelc_won_MYS_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_MYS_003</t>
   </si>
   <si>
@@ -1018,27 +1018,69 @@
     <t>connecting wind onshore to buses in cluster 5</t>
   </si>
   <si>
+    <t>elc_won_MYS_002</t>
+  </si>
+  <si>
+    <t>e_w450080688-275_MYS</t>
+  </si>
+  <si>
     <t>elc_won_MYS_001</t>
   </si>
   <si>
-    <t>e_w450080688-275_MYS</t>
-  </si>
-  <si>
     <t>elc_won_MYS_004</t>
   </si>
   <si>
     <t>elc_won_MYS_006</t>
   </si>
   <si>
-    <t>elc_won_MYS_002</t>
-  </si>
-  <si>
     <t>elc_won_MYS_003</t>
   </si>
   <si>
     <t>elc_won_MYS_005</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_MYS_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_MYS_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_MYS_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_MYS_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_MYS_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_MYS_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_MYS_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_MYS_008</t>
   </si>
   <si>
@@ -1057,46 +1099,37 @@
     <t>connecting wind offshore to buses in cluster 7</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_MYS_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_MYS_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_MYS_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_MYS_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_MYS_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_MYS_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_MYS_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
+    <t>elc_wof_MYS_009</t>
+  </si>
+  <si>
+    <t>elc_wof_MYS_002</t>
+  </si>
+  <si>
+    <t>e_w552780098-275_MYS</t>
+  </si>
+  <si>
+    <t>elc_wof_MYS_004</t>
+  </si>
+  <si>
+    <t>elc_wof_MYS_003</t>
+  </si>
+  <si>
+    <t>e_w552780098-275_MYS,e_w552820941-275_MYS</t>
+  </si>
+  <si>
+    <t>elc_wof_MYS_001</t>
+  </si>
+  <si>
+    <t>e_w235966081-275_MYS,e_w1137665609-275_MYS</t>
+  </si>
+  <si>
+    <t>elc_wof_MYS_010</t>
+  </si>
+  <si>
+    <t>e_w562298165-275_MYS,e_w450080688-275_MYS</t>
+  </si>
+  <si>
+    <t>elc_wof_MYS_005</t>
   </si>
   <si>
     <t>elc_wof_MYS_008</t>
@@ -1112,39 +1145,6 @@
   </si>
   <si>
     <t>e_w513950834-275_MYS</t>
-  </si>
-  <si>
-    <t>elc_wof_MYS_009</t>
-  </si>
-  <si>
-    <t>elc_wof_MYS_003</t>
-  </si>
-  <si>
-    <t>e_w552780098-275_MYS,e_w552820941-275_MYS</t>
-  </si>
-  <si>
-    <t>elc_wof_MYS_001</t>
-  </si>
-  <si>
-    <t>e_w235966081-275_MYS,e_w1137665609-275_MYS</t>
-  </si>
-  <si>
-    <t>elc_wof_MYS_010</t>
-  </si>
-  <si>
-    <t>e_w562298165-275_MYS,e_w450080688-275_MYS</t>
-  </si>
-  <si>
-    <t>elc_wof_MYS_005</t>
-  </si>
-  <si>
-    <t>elc_wof_MYS_002</t>
-  </si>
-  <si>
-    <t>e_w552780098-275_MYS</t>
-  </si>
-  <si>
-    <t>elc_wof_MYS_004</t>
   </si>
   <si>
     <t>e_won_MYS_001</t>
@@ -6251,7 +6251,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B8DFA56-FE84-422C-BFB2-F1821FF4761C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EBFBA69-5FAF-48A4-B852-17E07E94189D}">
   <dimension ref="B9:BD27"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6489,16 +6489,16 @@
         <v>232</v>
       </c>
       <c r="Y11" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="Z11" t="s">
         <v>270</v>
       </c>
       <c r="AA11">
-        <v>0.99510897523885211</v>
+        <v>0.99814918620633797</v>
       </c>
       <c r="AB11">
-        <v>89.668787287710401</v>
+        <v>33.931586217137827</v>
       </c>
       <c r="AD11" t="s">
         <v>231</v>
@@ -6531,10 +6531,10 @@
         <v>297</v>
       </c>
       <c r="AO11">
-        <v>0.99707574038447433</v>
+        <v>0.99555745609122392</v>
       </c>
       <c r="AP11">
-        <v>53.611426284636785</v>
+        <v>81.446638327560734</v>
       </c>
       <c r="AR11" t="s">
         <v>231</v>
@@ -6564,13 +6564,13 @@
         <v>323</v>
       </c>
       <c r="BB11" t="s">
-        <v>324</v>
+        <v>297</v>
       </c>
       <c r="BC11">
-        <v>0.97644633349267118</v>
+        <v>0.98051979717181825</v>
       </c>
       <c r="BD11">
-        <v>431.81721930102793</v>
+        <v>357.13705184999884</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -6635,16 +6635,16 @@
         <v>236</v>
       </c>
       <c r="Y12" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="Z12" t="s">
         <v>271</v>
       </c>
       <c r="AA12">
-        <v>0.99290727743954299</v>
+        <v>0.99788440132737488</v>
       </c>
       <c r="AB12">
-        <v>130.03324694171172</v>
+        <v>38.785975664794165</v>
       </c>
       <c r="AD12" t="s">
         <v>231</v>
@@ -6677,10 +6677,10 @@
         <v>297</v>
       </c>
       <c r="AO12">
-        <v>0.99181427590511306</v>
+        <v>0.99707574038447433</v>
       </c>
       <c r="AP12">
-        <v>150.07160840625986</v>
+        <v>53.611426284636785</v>
       </c>
       <c r="AR12" t="s">
         <v>231</v>
@@ -6707,16 +6707,16 @@
         <v>305</v>
       </c>
       <c r="BA12" t="s">
+        <v>324</v>
+      </c>
+      <c r="BB12" t="s">
         <v>325</v>
       </c>
-      <c r="BB12" t="s">
-        <v>297</v>
-      </c>
       <c r="BC12">
-        <v>0.98985596153199862</v>
+        <v>0.98500048755641589</v>
       </c>
       <c r="BD12">
-        <v>185.97403858002539</v>
+        <v>274.9910614657079</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -6781,16 +6781,16 @@
         <v>238</v>
       </c>
       <c r="Y13" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Z13" t="s">
         <v>272</v>
       </c>
       <c r="AA13">
-        <v>0.99742316095831862</v>
+        <v>0.99857026813386185</v>
       </c>
       <c r="AB13">
-        <v>47.242049097491972</v>
+        <v>26.21175087919962</v>
       </c>
       <c r="AD13" t="s">
         <v>231</v>
@@ -6820,13 +6820,13 @@
         <v>299</v>
       </c>
       <c r="AN13" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="AO13">
-        <v>0.99124474077666069</v>
+        <v>0.99181427590511306</v>
       </c>
       <c r="AP13">
-        <v>160.51308576122122</v>
+        <v>150.07160840625986</v>
       </c>
       <c r="AR13" t="s">
         <v>231</v>
@@ -6856,13 +6856,13 @@
         <v>326</v>
       </c>
       <c r="BB13" t="s">
-        <v>327</v>
+        <v>297</v>
       </c>
       <c r="BC13">
-        <v>0.98322281233462283</v>
+        <v>0.9926406959075802</v>
       </c>
       <c r="BD13">
-        <v>307.58177386524892</v>
+        <v>134.92057502769742</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -6927,16 +6927,16 @@
         <v>240</v>
       </c>
       <c r="Y14" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Z14" t="s">
         <v>273</v>
       </c>
       <c r="AA14">
-        <v>0.99833039272231761</v>
+        <v>0.99510897523885211</v>
       </c>
       <c r="AB14">
-        <v>30.609466757511377</v>
+        <v>89.668787287710401</v>
       </c>
       <c r="AD14" t="s">
         <v>231</v>
@@ -6966,13 +6966,13 @@
         <v>300</v>
       </c>
       <c r="AN14" t="s">
-        <v>297</v>
+        <v>282</v>
       </c>
       <c r="AO14">
-        <v>0.99555745609122392</v>
+        <v>0.99124474077666069</v>
       </c>
       <c r="AP14">
-        <v>81.446638327560734</v>
+        <v>160.51308576122122</v>
       </c>
       <c r="AR14" t="s">
         <v>231</v>
@@ -6999,16 +6999,16 @@
         <v>309</v>
       </c>
       <c r="BA14" t="s">
+        <v>327</v>
+      </c>
+      <c r="BB14" t="s">
         <v>328</v>
       </c>
-      <c r="BB14" t="s">
-        <v>297</v>
-      </c>
       <c r="BC14">
-        <v>0.98051979717181825</v>
+        <v>0.98349999607155203</v>
       </c>
       <c r="BD14">
-        <v>357.13705184999884</v>
+        <v>302.50007202154563</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -7073,16 +7073,16 @@
         <v>242</v>
       </c>
       <c r="Y15" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="Z15" t="s">
         <v>274</v>
       </c>
       <c r="AA15">
-        <v>0.99124301005043802</v>
+        <v>0.99404697115518426</v>
       </c>
       <c r="AB15">
-        <v>160.54481574197013</v>
+        <v>109.13886215495538</v>
       </c>
       <c r="AD15" t="s">
         <v>231</v>
@@ -7151,10 +7151,10 @@
         <v>330</v>
       </c>
       <c r="BC15">
-        <v>0.98349999607155203</v>
+        <v>0.9731327844491402</v>
       </c>
       <c r="BD15">
-        <v>302.50007202154563</v>
+        <v>492.56561843243048</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -7219,16 +7219,16 @@
         <v>244</v>
       </c>
       <c r="Y16" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="Z16" t="s">
         <v>275</v>
       </c>
       <c r="AA16">
-        <v>0.99857026813386185</v>
+        <v>0.99641029170642137</v>
       </c>
       <c r="AB16">
-        <v>26.21175087919962</v>
+        <v>65.811318715607285</v>
       </c>
       <c r="AD16" t="s">
         <v>231</v>
@@ -7258,7 +7258,7 @@
         <v>302</v>
       </c>
       <c r="AN16" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AO16">
         <v>0.99023545286734149</v>
@@ -7297,10 +7297,10 @@
         <v>332</v>
       </c>
       <c r="BC16">
-        <v>0.9731327844491402</v>
+        <v>0.98197790527844686</v>
       </c>
       <c r="BD16">
-        <v>492.56561843243048</v>
+        <v>330.40506989514142</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -7365,16 +7365,16 @@
         <v>246</v>
       </c>
       <c r="Y17" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="Z17" t="s">
         <v>276</v>
       </c>
       <c r="AA17">
-        <v>0.99814918620633797</v>
+        <v>0.99822394178768203</v>
       </c>
       <c r="AB17">
-        <v>33.931586217137827</v>
+        <v>32.561067225829298</v>
       </c>
       <c r="AR17" t="s">
         <v>231</v>
@@ -7404,13 +7404,13 @@
         <v>333</v>
       </c>
       <c r="BB17" t="s">
-        <v>334</v>
+        <v>297</v>
       </c>
       <c r="BC17">
-        <v>0.98197790527844686</v>
+        <v>0.98911418404428342</v>
       </c>
       <c r="BD17">
-        <v>330.40506989514142</v>
+        <v>199.57329252147068</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -7475,16 +7475,16 @@
         <v>248</v>
       </c>
       <c r="Y18" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Z18" t="s">
         <v>277</v>
       </c>
       <c r="AA18">
-        <v>0.99788440132737488</v>
+        <v>0.99742316095831862</v>
       </c>
       <c r="AB18">
-        <v>38.785975664794165</v>
+        <v>47.242049097491972</v>
       </c>
       <c r="AR18" t="s">
         <v>231</v>
@@ -7511,16 +7511,16 @@
         <v>317</v>
       </c>
       <c r="BA18" t="s">
+        <v>334</v>
+      </c>
+      <c r="BB18" t="s">
         <v>335</v>
       </c>
-      <c r="BB18" t="s">
-        <v>297</v>
-      </c>
       <c r="BC18">
-        <v>0.98911418404428342</v>
+        <v>0.97644633349267118</v>
       </c>
       <c r="BD18">
-        <v>199.57329252147068</v>
+        <v>431.81721930102793</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -7585,16 +7585,16 @@
         <v>250</v>
       </c>
       <c r="Y19" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="Z19" t="s">
         <v>278</v>
       </c>
       <c r="AA19">
-        <v>0.99822394178768203</v>
+        <v>0.99833039272231761</v>
       </c>
       <c r="AB19">
-        <v>32.561067225829298</v>
+        <v>30.609466757511377</v>
       </c>
       <c r="AR19" t="s">
         <v>231</v>
@@ -7624,13 +7624,13 @@
         <v>336</v>
       </c>
       <c r="BB19" t="s">
-        <v>337</v>
+        <v>297</v>
       </c>
       <c r="BC19">
-        <v>0.98500048755641589</v>
+        <v>0.98985596153199862</v>
       </c>
       <c r="BD19">
-        <v>274.9910614657079</v>
+        <v>185.97403858002539</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -7695,16 +7695,16 @@
         <v>252</v>
       </c>
       <c r="Y20" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Z20" t="s">
         <v>279</v>
       </c>
       <c r="AA20">
-        <v>0.99541857140439349</v>
+        <v>0.99124301005043802</v>
       </c>
       <c r="AB20">
-        <v>83.992857586119158</v>
+        <v>160.54481574197013</v>
       </c>
       <c r="AR20" t="s">
         <v>231</v>
@@ -7731,16 +7731,16 @@
         <v>321</v>
       </c>
       <c r="BA20" t="s">
+        <v>337</v>
+      </c>
+      <c r="BB20" t="s">
         <v>338</v>
       </c>
-      <c r="BB20" t="s">
-        <v>297</v>
-      </c>
       <c r="BC20">
-        <v>0.9926406959075802</v>
+        <v>0.98322281233462283</v>
       </c>
       <c r="BD20">
-        <v>134.92057502769742</v>
+        <v>307.58177386524892</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -7805,16 +7805,16 @@
         <v>254</v>
       </c>
       <c r="Y21" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="Z21" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="AA21">
-        <v>0.9940167733084464</v>
+        <v>0.99290727743954299</v>
       </c>
       <c r="AB21">
-        <v>109.69248934514933</v>
+        <v>130.03324694171172</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -7879,16 +7879,16 @@
         <v>256</v>
       </c>
       <c r="Y22" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="Z22" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AA22">
-        <v>0.9970455298234584</v>
+        <v>0.99792831960738038</v>
       </c>
       <c r="AB22">
-        <v>54.165286569929123</v>
+        <v>37.980807198026596</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -7953,16 +7953,16 @@
         <v>258</v>
       </c>
       <c r="Y23" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Z23" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="AA23">
-        <v>0.99388261520871601</v>
+        <v>0.9940167733084464</v>
       </c>
       <c r="AB23">
-        <v>112.15205450687272</v>
+        <v>109.69248934514933</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -8027,16 +8027,16 @@
         <v>260</v>
       </c>
       <c r="Y24" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Z24" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AA24">
-        <v>0.99301257726365455</v>
+        <v>0.99541857140439349</v>
       </c>
       <c r="AB24">
-        <v>128.1027501663325</v>
+        <v>83.992857586119158</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -8101,16 +8101,16 @@
         <v>262</v>
       </c>
       <c r="Y25" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="Z25" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AA25">
-        <v>0.99792831960738038</v>
+        <v>0.99301257726365455</v>
       </c>
       <c r="AB25">
-        <v>37.980807198026596</v>
+        <v>128.1027501663325</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -8175,16 +8175,16 @@
         <v>264</v>
       </c>
       <c r="Y26" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="Z26" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AA26">
-        <v>0.99404697115518426</v>
+        <v>0.9970455298234584</v>
       </c>
       <c r="AB26">
-        <v>109.13886215495538</v>
+        <v>54.165286569929123</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -8249,16 +8249,16 @@
         <v>266</v>
       </c>
       <c r="Y27" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="Z27" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="AA27">
-        <v>0.99641029170642137</v>
+        <v>0.99388261520871601</v>
       </c>
       <c r="AB27">
-        <v>65.811318715607285</v>
+        <v>112.15205450687272</v>
       </c>
     </row>
   </sheetData>
@@ -8267,7 +8267,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16C70D55-42F3-400D-A607-37C5AE7259B8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B83D7E3-5C4E-494E-9B6B-308BC488DCE8}">
   <dimension ref="B9:Z20"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -8379,7 +8379,7 @@
         <v>339</v>
       </c>
       <c r="K11" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="L11">
         <v>5.3956320681287483E-3</v>
@@ -8412,7 +8412,7 @@
         <v>351</v>
       </c>
       <c r="X11" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="Y11">
         <v>1.9035</v>
@@ -8447,7 +8447,7 @@
         <v>341</v>
       </c>
       <c r="K12" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="L12">
         <v>3.4940612871927561E-2</v>
@@ -8480,7 +8480,7 @@
         <v>353</v>
       </c>
       <c r="X12" t="s">
-        <v>336</v>
+        <v>324</v>
       </c>
       <c r="Y12">
         <v>1.0927500000000001</v>
@@ -8548,7 +8548,7 @@
         <v>355</v>
       </c>
       <c r="X13" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="Y13">
         <v>3.08175</v>
@@ -8583,7 +8583,7 @@
         <v>345</v>
       </c>
       <c r="K14" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L14">
         <v>0.28646033146389088</v>
@@ -8616,7 +8616,7 @@
         <v>357</v>
       </c>
       <c r="X14" t="s">
-        <v>338</v>
+        <v>326</v>
       </c>
       <c r="Y14">
         <v>7.6124999999999998</v>
@@ -8684,7 +8684,7 @@
         <v>359</v>
       </c>
       <c r="X15" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="Y15">
         <v>7.6687500000000002</v>
@@ -8719,7 +8719,7 @@
         <v>349</v>
       </c>
       <c r="K16" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L16">
         <v>1.1234616966489041E-2</v>
@@ -8752,7 +8752,7 @@
         <v>361</v>
       </c>
       <c r="X16" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="Y16">
         <v>2.4397500000000001</v>
@@ -8787,7 +8787,7 @@
         <v>363</v>
       </c>
       <c r="X17" t="s">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="Y17">
         <v>0.189</v>
@@ -8822,7 +8822,7 @@
         <v>365</v>
       </c>
       <c r="X18" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="Y18">
         <v>5.9077500000000001</v>
@@ -8857,7 +8857,7 @@
         <v>367</v>
       </c>
       <c r="X19" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="Y19">
         <v>3.9195000000000002</v>
@@ -8892,7 +8892,7 @@
         <v>369</v>
       </c>
       <c r="X20" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="Y20">
         <v>7.3425000000000002</v>
@@ -8907,7 +8907,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8235513-6312-4196-A38E-95F7A7694773}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85642FD6-D606-4145-B5AC-EFA2DFDEDB0B}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -10724,7 +10724,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15C56C61-73F8-45BD-9367-D0E391603307}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E66F7586-3D6C-4951-9AB3-F0DF5F3738FD}">
   <dimension ref="B2:M25"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_MYS_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_MYS_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_MYS_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D1082310-C008-4282-BDB5-7C44B7D81792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F5B29418-AA75-4B7B-9F7E-A213DB32DF38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1623" uniqueCount="463">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1839" uniqueCount="534">
   <si>
     <t>~FI_Process</t>
   </si>
@@ -757,6 +757,48 @@
     <t>solar resource in cluster 17</t>
   </si>
   <si>
+    <t>e_spv_MYS_018</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 18</t>
+  </si>
+  <si>
+    <t>e_spv_MYS_019</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 19</t>
+  </si>
+  <si>
+    <t>e_spv_MYS_020</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 20</t>
+  </si>
+  <si>
+    <t>e_spv_MYS_021</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 21</t>
+  </si>
+  <si>
+    <t>e_spv_MYS_022</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 22</t>
+  </si>
+  <si>
+    <t>e_spv_MYS_023</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 23</t>
+  </si>
+  <si>
+    <t>e_spv_MYS_024</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 24</t>
+  </si>
+  <si>
     <t>~fi_t</t>
   </si>
   <si>
@@ -820,28 +862,169 @@
     <t>elc_spv_MYS_017</t>
   </si>
   <si>
+    <t>elc_spv_MYS_018</t>
+  </si>
+  <si>
+    <t>elc_spv_MYS_019</t>
+  </si>
+  <si>
+    <t>elc_spv_MYS_020</t>
+  </si>
+  <si>
+    <t>elc_spv_MYS_021</t>
+  </si>
+  <si>
+    <t>elc_spv_MYS_022</t>
+  </si>
+  <si>
+    <t>elc_spv_MYS_023</t>
+  </si>
+  <si>
+    <t>elc_spv_MYS_024</t>
+  </si>
+  <si>
     <t>primarycg</t>
   </si>
   <si>
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_MYS_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MYS_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MYS_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MYS_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MYS_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MYS_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MYS_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MYS_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MYS_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MYS_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MYS_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MYS_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MYS_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MYS_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MYS_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MYS_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MYS_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_MYS_010</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 10</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MYS_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
+    <t>distr_solelc_spv_MYS_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MYS_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MYS_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MYS_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
   </si>
   <si>
     <t>distr_solelc_spv_MYS_009</t>
@@ -850,84 +1033,6 @@
     <t>connecting solar to buses in cluster 9</t>
   </si>
   <si>
-    <t>distr_solelc_spv_MYS_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MYS_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MYS_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MYS_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MYS_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MYS_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MYS_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MYS_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MYS_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MYS_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MYS_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MYS_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MYS_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_MYS_014</t>
   </si>
   <si>
@@ -940,46 +1045,82 @@
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
-    <t>e_w691239971-275_MYS,e_w325835238-275_MYS,e_MY68-275_MYS,e_w561806959-275_MYS,e_w399307646-275_MYS,e_w320246940-275_MYS</t>
-  </si>
-  <si>
-    <t>e_w399307647-275_MYS,e_w1137665609-275_MYS,e_w691633793-275_MYS,e_w691633796-275_MYS,e_w513610290-275_MYS</t>
-  </si>
-  <si>
-    <t>e_MY68-275_MYS,e_w561806959-275_MYS,e_w934653890-275_MYS</t>
+    <t>e_w450080688-275_MYS,e_w328415531-275_MYS</t>
+  </si>
+  <si>
+    <t>e_w552579228-275_MYS,e_w316035705-500_MYS,e_w552589219-275_MYS,e_MY27-275_MYS</t>
+  </si>
+  <si>
+    <t>e_w1324718458-275_MYS,e_MY20-275_MYS,e_MY13-275_MYS,e_w460916219-275_MYS,e_w316035698-500_MYS,e_MY21-275_MYS,e_MY14-275_MYS,e_w556802417-275_MYS</t>
+  </si>
+  <si>
+    <t>e_w691633793-275_MYS,e_w691633796-275_MYS,e_w513610290-275_MYS,e_w236051516-275_MYS,e_w1137665615-275_MYS</t>
+  </si>
+  <si>
+    <t>e_w286559638-275_MYS,e_w326097227-275_MYS,e_w286559640-275_MYS,e_MY2-275_MYS</t>
+  </si>
+  <si>
+    <t>e_w235851822-500_MYS,e_MY64-275_MYS,e_MY76-275_MYS,e_w755608493-275_MYS,e_w496114385-275_MYS</t>
+  </si>
+  <si>
+    <t>e_MY59-275_MYS,e_w1137665620-500_MYS</t>
+  </si>
+  <si>
+    <t>e_w320730394-275_MYS,e_MY5-275_MYS,e_MY4-275_MYS,e_w755391602-275_MYS</t>
+  </si>
+  <si>
+    <t>e_w755391602-275_MYS,e_MY17-275_MYS,e_MY3-275_MYS,e_w552820941-275_MYS,e_w552681748-275_MYS,e_MY18-275_MYS,e_w755700380-275_MYS,e_w552780098-275_MYS</t>
+  </si>
+  <si>
+    <t>e_w561806959-275_MYS,e_w235966081-275_MYS,e_w399307647-275_MYS,e_w1137665609-275_MYS</t>
+  </si>
+  <si>
+    <t>e_MY27-275_MYS,e_w755036990-275_MYS,e_w317124038-275_MYS,e_MY26-275_MYS,e_w885845346-275_MYS,e_w662315251-275_MYS</t>
+  </si>
+  <si>
+    <t>e_w553040556-275_MYS,e_w662315251-275_MYS,e_w892365043-275_MYS,e_MY18-275_MYS</t>
+  </si>
+  <si>
+    <t>e_w691200886-275_MYS,e_w235943019-275_MYS,e_w235951698-275_MYS,e_w691239971-275_MYS,e_w325835238-275_MYS,e_MY68-275_MYS</t>
+  </si>
+  <si>
+    <t>e_MY16-275_MYS,e_MY12-275_MYS,e_w450080688-275_MYS,e_w328415531-275_MYS</t>
+  </si>
+  <si>
+    <t>e_w492388990-275_MYS,e_MY46-275_MYS,e_MY61-275_MYS,e_MY52-275_MYS,e_w1137308780-275_MYS,e_w553040556-275_MYS,e_w1137308780-500_MYS</t>
+  </si>
+  <si>
+    <t>e_w691239971-275_MYS,e_w399307646-275_MYS,e_MY68-275_MYS,e_w320246940-275_MYS,e_w934653890-275_MYS</t>
+  </si>
+  <si>
+    <t>e_w554295894-275_MYS,e_w554938963-275_MYS,e_w553339782-275_MYS,e_w445431079-275_MYS,e_w1137308780-500_MYS,e_w755668283-500_MYS,e_w755668283-275_MYS,e_w235501402-500_MYS,e_MY63-275_MYS</t>
+  </si>
+  <si>
+    <t>e_MY59-275_MYS</t>
+  </si>
+  <si>
+    <t>e_w1137308780-500_MYS,e_w559750680-275_MYS,e_w396464338-275_MYS,e_w235501402-500_MYS,e_w496114385-275_MYS</t>
+  </si>
+  <si>
+    <t>e_w1285211558-275_MYS,e_w562298165-275_MYS,e_MY12-275_MYS,e_w450080688-275_MYS</t>
+  </si>
+  <si>
+    <t>e_MY25-500_MYS,e_w1137665617-275_MYS,e_w1137665620-500_MYS,e_w513950834-275_MYS</t>
   </si>
   <si>
     <t>e_w1137665620-500_MYS,e_w513950834-275_MYS,e_w1285211558-275_MYS,e_MY16-275_MYS</t>
   </si>
   <si>
-    <t>e_MY59-275_MYS</t>
-  </si>
-  <si>
-    <t>e_w450080688-275_MYS,e_w328415531-275_MYS</t>
-  </si>
-  <si>
-    <t>e_MY25-500_MYS,e_w1137665617-275_MYS,e_w1137665620-500_MYS,e_w513950834-275_MYS</t>
-  </si>
-  <si>
-    <t>e_w691200886-275_MYS,e_w235943019-275_MYS,e_w235951698-275_MYS</t>
-  </si>
-  <si>
-    <t>e_w1285211558-275_MYS,e_w562298165-275_MYS,e_MY12-275_MYS,e_w450080688-275_MYS</t>
-  </si>
-  <si>
-    <t>e_MY16-275_MYS,e_MY12-275_MYS,e_w328415531-275_MYS</t>
-  </si>
-  <si>
-    <t>e_w236051516-275_MYS,e_w513610290-275_MYS,e_w1137665615-275_MYS,e_MY59-275_MYS,e_w1137665620-500_MYS</t>
-  </si>
-  <si>
     <t>e_w320246940-275_MYS,e_w934653890-275_MYS,e_w513610290-275_MYS</t>
   </si>
   <si>
     <t>e_w328415531-275_MYS</t>
   </si>
   <si>
-    <t>e_w561806959-275_MYS,e_w235966081-275_MYS</t>
+    <t>distr_wonelc_won_MYS_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
   </si>
   <si>
     <t>distr_wonelc_won_MYS_002</t>
@@ -988,22 +1129,46 @@
     <t>connecting wind onshore to buses in cluster 2</t>
   </si>
   <si>
+    <t>distr_wonelc_won_MYS_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_MYS_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_MYS_001</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 1</t>
   </si>
   <si>
+    <t>distr_wonelc_won_MYS_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_MYS_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_MYS_004</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 4</t>
   </si>
   <si>
-    <t>distr_wonelc_won_MYS_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
+    <t>distr_wonelc_won_MYS_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
   </si>
   <si>
     <t>distr_wonelc_won_MYS_003</t>
@@ -1012,10 +1177,10 @@
     <t>connecting wind onshore to buses in cluster 3</t>
   </si>
   <si>
-    <t>distr_wonelc_won_MYS_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
+    <t>elc_won_MYS_007</t>
+  </si>
+  <si>
+    <t>e_w286559638-275_MYS</t>
   </si>
   <si>
     <t>elc_won_MYS_002</t>
@@ -1024,19 +1189,97 @@
     <t>e_w450080688-275_MYS</t>
   </si>
   <si>
+    <t>elc_won_MYS_010</t>
+  </si>
+  <si>
+    <t>e_w559750680-275_MYS,e_w396464338-275_MYS</t>
+  </si>
+  <si>
+    <t>elc_won_MYS_008</t>
+  </si>
+  <si>
+    <t>e_w755700380-275_MYS,e_w552780098-275_MYS</t>
+  </si>
+  <si>
     <t>elc_won_MYS_001</t>
   </si>
   <si>
+    <t>elc_won_MYS_006</t>
+  </si>
+  <si>
+    <t>elc_won_MYS_005</t>
+  </si>
+  <si>
+    <t>e_w235851822-500_MYS,e_MY76-275_MYS</t>
+  </si>
+  <si>
     <t>elc_won_MYS_004</t>
   </si>
   <si>
-    <t>elc_won_MYS_006</t>
+    <t>e_w755608493-275_MYS,e_w496114385-275_MYS,e_MY76-275_MYS</t>
+  </si>
+  <si>
+    <t>elc_won_MYS_009</t>
+  </si>
+  <si>
+    <t>e_w235501402-500_MYS,e_w559750680-275_MYS,e_w496114385-275_MYS</t>
   </si>
   <si>
     <t>elc_won_MYS_003</t>
   </si>
   <si>
-    <t>elc_won_MYS_005</t>
+    <t>distr_wofelc_wof_MYS_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_MYS_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_MYS_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_MYS_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_MYS_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_MYS_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_MYS_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_MYS_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_MYS_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
   </si>
   <si>
     <t>distr_wofelc_wof_MYS_009</t>
@@ -1045,108 +1288,54 @@
     <t>connecting wind offshore to buses in cluster 9</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_MYS_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_MYS_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_MYS_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_MYS_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_MYS_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_MYS_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_MYS_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_MYS_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_MYS_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
+    <t>elc_wof_MYS_007</t>
+  </si>
+  <si>
+    <t>e_w513950834-275_MYS</t>
+  </si>
+  <si>
+    <t>elc_wof_MYS_003</t>
+  </si>
+  <si>
+    <t>e_w552780098-275_MYS,e_w552820941-275_MYS</t>
+  </si>
+  <si>
+    <t>elc_wof_MYS_001</t>
+  </si>
+  <si>
+    <t>e_w235966081-275_MYS,e_w1137665609-275_MYS</t>
+  </si>
+  <si>
+    <t>elc_wof_MYS_010</t>
+  </si>
+  <si>
+    <t>e_w562298165-275_MYS,e_w450080688-275_MYS</t>
+  </si>
+  <si>
+    <t>elc_wof_MYS_005</t>
+  </si>
+  <si>
+    <t>elc_wof_MYS_002</t>
+  </si>
+  <si>
+    <t>e_w552780098-275_MYS</t>
+  </si>
+  <si>
+    <t>elc_wof_MYS_004</t>
+  </si>
+  <si>
+    <t>elc_wof_MYS_008</t>
+  </si>
+  <si>
+    <t>e_w513950834-275_MYS,e_w562298165-275_MYS,e_w450080688-275_MYS</t>
+  </si>
+  <si>
+    <t>elc_wof_MYS_006</t>
   </si>
   <si>
     <t>elc_wof_MYS_009</t>
   </si>
   <si>
-    <t>elc_wof_MYS_002</t>
-  </si>
-  <si>
-    <t>e_w552780098-275_MYS</t>
-  </si>
-  <si>
-    <t>elc_wof_MYS_004</t>
-  </si>
-  <si>
-    <t>elc_wof_MYS_003</t>
-  </si>
-  <si>
-    <t>e_w552780098-275_MYS,e_w552820941-275_MYS</t>
-  </si>
-  <si>
-    <t>elc_wof_MYS_001</t>
-  </si>
-  <si>
-    <t>e_w235966081-275_MYS,e_w1137665609-275_MYS</t>
-  </si>
-  <si>
-    <t>elc_wof_MYS_010</t>
-  </si>
-  <si>
-    <t>e_w562298165-275_MYS,e_w450080688-275_MYS</t>
-  </si>
-  <si>
-    <t>elc_wof_MYS_005</t>
-  </si>
-  <si>
-    <t>elc_wof_MYS_008</t>
-  </si>
-  <si>
-    <t>e_w513950834-275_MYS,e_w562298165-275_MYS,e_w450080688-275_MYS</t>
-  </si>
-  <si>
-    <t>elc_wof_MYS_006</t>
-  </si>
-  <si>
-    <t>elc_wof_MYS_007</t>
-  </si>
-  <si>
-    <t>e_w513950834-275_MYS</t>
-  </si>
-  <si>
     <t>e_won_MYS_001</t>
   </si>
   <si>
@@ -1181,6 +1370,30 @@
   </si>
   <si>
     <t>wind resource in cluster 6</t>
+  </si>
+  <si>
+    <t>e_won_MYS_007</t>
+  </si>
+  <si>
+    <t>wind resource in cluster 7</t>
+  </si>
+  <si>
+    <t>e_won_MYS_008</t>
+  </si>
+  <si>
+    <t>wind resource in cluster 8</t>
+  </si>
+  <si>
+    <t>e_won_MYS_009</t>
+  </si>
+  <si>
+    <t>wind resource in cluster 9</t>
+  </si>
+  <si>
+    <t>e_won_MYS_010</t>
+  </si>
+  <si>
+    <t>wind resource in cluster 10</t>
   </si>
   <si>
     <t>e_wof_MYS_001</t>
@@ -3450,7 +3663,7 @@
         <v>50</v>
       </c>
       <c r="V28" s="147" t="s">
-        <v>462</v>
+        <v>533</v>
       </c>
     </row>
   </sheetData>
@@ -6251,8 +6464,8 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EBFBA69-5FAF-48A4-B852-17E07E94189D}">
-  <dimension ref="B9:BD27"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0D4D9A6-9FBC-4B60-A6C9-731964BC69D9}">
+  <dimension ref="B9:BD34"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="9" spans="2:56">
@@ -6260,25 +6473,25 @@
         <v>164</v>
       </c>
       <c r="J9" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="O9" t="s">
         <v>164</v>
       </c>
       <c r="X9" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="AD9" t="s">
         <v>164</v>
       </c>
       <c r="AL9" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="AR9" t="s">
         <v>164</v>
       </c>
       <c r="AZ9" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
     </row>
     <row r="10" spans="2:56">
@@ -6307,13 +6520,13 @@
         <v>166</v>
       </c>
       <c r="K10" t="s">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="L10" t="s">
-        <v>211</v>
+        <v>225</v>
       </c>
       <c r="M10" t="s">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="O10" t="s">
         <v>165</v>
@@ -6331,7 +6544,7 @@
         <v>169</v>
       </c>
       <c r="T10" t="s">
-        <v>230</v>
+        <v>251</v>
       </c>
       <c r="U10" t="s">
         <v>170</v>
@@ -6343,16 +6556,16 @@
         <v>166</v>
       </c>
       <c r="Y10" t="s">
-        <v>268</v>
+        <v>303</v>
       </c>
       <c r="Z10" t="s">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="AA10" t="s">
         <v>146</v>
       </c>
       <c r="AB10" t="s">
-        <v>269</v>
+        <v>304</v>
       </c>
       <c r="AD10" t="s">
         <v>165</v>
@@ -6379,16 +6592,16 @@
         <v>166</v>
       </c>
       <c r="AM10" t="s">
-        <v>268</v>
+        <v>303</v>
       </c>
       <c r="AN10" t="s">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="AO10" t="s">
         <v>146</v>
       </c>
       <c r="AP10" t="s">
-        <v>269</v>
+        <v>304</v>
       </c>
       <c r="AR10" t="s">
         <v>165</v>
@@ -6415,16 +6628,16 @@
         <v>166</v>
       </c>
       <c r="BA10" t="s">
-        <v>268</v>
+        <v>303</v>
       </c>
       <c r="BB10" t="s">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="BC10" t="s">
         <v>146</v>
       </c>
       <c r="BD10" t="s">
-        <v>269</v>
+        <v>304</v>
       </c>
     </row>
     <row r="11" spans="2:56">
@@ -6453,22 +6666,22 @@
         <v>173</v>
       </c>
       <c r="K11" t="s">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="L11">
-        <v>13.022147720700652</v>
+        <v>5.2573773157855594</v>
       </c>
       <c r="M11">
-        <v>0.1925977921041597</v>
+        <v>0.18597024783276719</v>
       </c>
       <c r="O11" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="P11" t="s">
-        <v>232</v>
+        <v>253</v>
       </c>
       <c r="Q11" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="R11" t="s">
         <v>10</v>
@@ -6477,37 +6690,37 @@
         <v>21</v>
       </c>
       <c r="T11" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="U11" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="V11" t="s">
         <v>176</v>
       </c>
       <c r="X11" t="s">
-        <v>232</v>
+        <v>253</v>
       </c>
       <c r="Y11" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="Z11" t="s">
-        <v>270</v>
+        <v>305</v>
       </c>
       <c r="AA11">
-        <v>0.99814918620633797</v>
+        <v>0.99610860481200558</v>
       </c>
       <c r="AB11">
-        <v>33.931586217137827</v>
+        <v>71.342245113231982</v>
       </c>
       <c r="AD11" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="AE11" t="s">
-        <v>284</v>
+        <v>329</v>
       </c>
       <c r="AF11" t="s">
-        <v>285</v>
+        <v>330</v>
       </c>
       <c r="AG11" t="s">
         <v>10</v>
@@ -6516,34 +6729,34 @@
         <v>21</v>
       </c>
       <c r="AI11" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="AJ11" t="s">
         <v>176</v>
       </c>
       <c r="AL11" t="s">
-        <v>284</v>
+        <v>329</v>
       </c>
       <c r="AM11" t="s">
-        <v>296</v>
+        <v>349</v>
       </c>
       <c r="AN11" t="s">
-        <v>297</v>
+        <v>350</v>
       </c>
       <c r="AO11">
-        <v>0.99555745609122392</v>
+        <v>0.99806527403456324</v>
       </c>
       <c r="AP11">
-        <v>81.446638327560734</v>
+        <v>35.469976033007349</v>
       </c>
       <c r="AR11" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="AS11" t="s">
-        <v>303</v>
+        <v>366</v>
       </c>
       <c r="AT11" t="s">
-        <v>304</v>
+        <v>367</v>
       </c>
       <c r="AU11" t="s">
         <v>10</v>
@@ -6552,25 +6765,25 @@
         <v>21</v>
       </c>
       <c r="AW11" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="AX11" t="s">
         <v>176</v>
       </c>
       <c r="AZ11" t="s">
-        <v>303</v>
+        <v>366</v>
       </c>
       <c r="BA11" t="s">
-        <v>323</v>
+        <v>386</v>
       </c>
       <c r="BB11" t="s">
-        <v>297</v>
+        <v>387</v>
       </c>
       <c r="BC11">
-        <v>0.98051979717181825</v>
+        <v>0.98322281233462283</v>
       </c>
       <c r="BD11">
-        <v>357.13705184999884</v>
+        <v>307.58177386524892</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -6599,22 +6812,22 @@
         <v>177</v>
       </c>
       <c r="K12" t="s">
-        <v>214</v>
+        <v>228</v>
       </c>
       <c r="L12">
-        <v>20.516577776215822</v>
+        <v>10.809349531262058</v>
       </c>
       <c r="M12">
-        <v>0.18343914249784479</v>
+        <v>0.19036526081330329</v>
       </c>
       <c r="O12" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="P12" t="s">
-        <v>236</v>
+        <v>257</v>
       </c>
       <c r="Q12" t="s">
-        <v>237</v>
+        <v>258</v>
       </c>
       <c r="R12" t="s">
         <v>10</v>
@@ -6623,37 +6836,37 @@
         <v>21</v>
       </c>
       <c r="T12" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="U12" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="V12" t="s">
         <v>176</v>
       </c>
       <c r="X12" t="s">
-        <v>236</v>
+        <v>257</v>
       </c>
       <c r="Y12" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="Z12" t="s">
-        <v>271</v>
+        <v>306</v>
       </c>
       <c r="AA12">
-        <v>0.99788440132737488</v>
+        <v>0.99765663107019265</v>
       </c>
       <c r="AB12">
-        <v>38.785975664794165</v>
+        <v>42.961763713135106</v>
       </c>
       <c r="AD12" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="AE12" t="s">
-        <v>286</v>
+        <v>331</v>
       </c>
       <c r="AF12" t="s">
-        <v>287</v>
+        <v>332</v>
       </c>
       <c r="AG12" t="s">
         <v>10</v>
@@ -6662,34 +6875,34 @@
         <v>21</v>
       </c>
       <c r="AI12" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="AJ12" t="s">
         <v>176</v>
       </c>
       <c r="AL12" t="s">
-        <v>286</v>
+        <v>331</v>
       </c>
       <c r="AM12" t="s">
-        <v>298</v>
+        <v>351</v>
       </c>
       <c r="AN12" t="s">
-        <v>297</v>
+        <v>352</v>
       </c>
       <c r="AO12">
-        <v>0.99707574038447433</v>
+        <v>0.99576055143223485</v>
       </c>
       <c r="AP12">
-        <v>53.611426284636785</v>
+        <v>77.723223742361768</v>
       </c>
       <c r="AR12" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="AS12" t="s">
-        <v>305</v>
+        <v>368</v>
       </c>
       <c r="AT12" t="s">
-        <v>306</v>
+        <v>369</v>
       </c>
       <c r="AU12" t="s">
         <v>10</v>
@@ -6698,25 +6911,25 @@
         <v>21</v>
       </c>
       <c r="AW12" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="AX12" t="s">
         <v>176</v>
       </c>
       <c r="AZ12" t="s">
-        <v>305</v>
+        <v>368</v>
       </c>
       <c r="BA12" t="s">
-        <v>324</v>
+        <v>388</v>
       </c>
       <c r="BB12" t="s">
-        <v>325</v>
+        <v>389</v>
       </c>
       <c r="BC12">
-        <v>0.98500048755641589</v>
+        <v>0.98349999607155203</v>
       </c>
       <c r="BD12">
-        <v>274.9910614657079</v>
+        <v>302.50007202154563</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -6745,22 +6958,22 @@
         <v>179</v>
       </c>
       <c r="K13" t="s">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="L13">
-        <v>7.5898506979633726</v>
+        <v>19.828489270063333</v>
       </c>
       <c r="M13">
-        <v>0.19798944902698659</v>
+        <v>0.18237867759777091</v>
       </c>
       <c r="O13" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="P13" t="s">
-        <v>238</v>
+        <v>259</v>
       </c>
       <c r="Q13" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
       <c r="R13" t="s">
         <v>10</v>
@@ -6769,37 +6982,37 @@
         <v>21</v>
       </c>
       <c r="T13" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="U13" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="V13" t="s">
         <v>176</v>
       </c>
       <c r="X13" t="s">
-        <v>238</v>
+        <v>259</v>
       </c>
       <c r="Y13" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="Z13" t="s">
-        <v>272</v>
+        <v>307</v>
       </c>
       <c r="AA13">
-        <v>0.99857026813386185</v>
+        <v>0.99923105930988987</v>
       </c>
       <c r="AB13">
-        <v>26.21175087919962</v>
+        <v>14.097245985353069</v>
       </c>
       <c r="AD13" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="AE13" t="s">
-        <v>288</v>
+        <v>333</v>
       </c>
       <c r="AF13" t="s">
-        <v>289</v>
+        <v>334</v>
       </c>
       <c r="AG13" t="s">
         <v>10</v>
@@ -6808,34 +7021,34 @@
         <v>21</v>
       </c>
       <c r="AI13" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="AJ13" t="s">
         <v>176</v>
       </c>
       <c r="AL13" t="s">
-        <v>288</v>
+        <v>333</v>
       </c>
       <c r="AM13" t="s">
-        <v>299</v>
+        <v>353</v>
       </c>
       <c r="AN13" t="s">
-        <v>297</v>
+        <v>354</v>
       </c>
       <c r="AO13">
-        <v>0.99181427590511306</v>
+        <v>0.99576941373570749</v>
       </c>
       <c r="AP13">
-        <v>150.07160840625986</v>
+        <v>77.560748178695945</v>
       </c>
       <c r="AR13" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="AS13" t="s">
-        <v>307</v>
+        <v>370</v>
       </c>
       <c r="AT13" t="s">
-        <v>308</v>
+        <v>371</v>
       </c>
       <c r="AU13" t="s">
         <v>10</v>
@@ -6844,25 +7057,25 @@
         <v>21</v>
       </c>
       <c r="AW13" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="AX13" t="s">
         <v>176</v>
       </c>
       <c r="AZ13" t="s">
-        <v>307</v>
+        <v>370</v>
       </c>
       <c r="BA13" t="s">
-        <v>326</v>
+        <v>390</v>
       </c>
       <c r="BB13" t="s">
-        <v>297</v>
+        <v>391</v>
       </c>
       <c r="BC13">
-        <v>0.9926406959075802</v>
+        <v>0.9731327844491402</v>
       </c>
       <c r="BD13">
-        <v>134.92057502769742</v>
+        <v>492.56561843243048</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -6891,22 +7104,22 @@
         <v>181</v>
       </c>
       <c r="K14" t="s">
-        <v>216</v>
+        <v>230</v>
       </c>
       <c r="L14">
-        <v>4.0975859847057476</v>
+        <v>28.760555259094438</v>
       </c>
       <c r="M14">
-        <v>0.1760540583973168</v>
+        <v>0.17262340982500191</v>
       </c>
       <c r="O14" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="P14" t="s">
-        <v>240</v>
+        <v>261</v>
       </c>
       <c r="Q14" t="s">
-        <v>241</v>
+        <v>262</v>
       </c>
       <c r="R14" t="s">
         <v>10</v>
@@ -6915,37 +7128,37 @@
         <v>21</v>
       </c>
       <c r="T14" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="U14" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="V14" t="s">
         <v>176</v>
       </c>
       <c r="X14" t="s">
-        <v>240</v>
+        <v>261</v>
       </c>
       <c r="Y14" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="Z14" t="s">
-        <v>273</v>
+        <v>308</v>
       </c>
       <c r="AA14">
-        <v>0.99510897523885211</v>
+        <v>0.9976124130534012</v>
       </c>
       <c r="AB14">
-        <v>89.668787287710401</v>
+        <v>43.772427354311056</v>
       </c>
       <c r="AD14" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="AE14" t="s">
-        <v>290</v>
+        <v>335</v>
       </c>
       <c r="AF14" t="s">
-        <v>291</v>
+        <v>336</v>
       </c>
       <c r="AG14" t="s">
         <v>10</v>
@@ -6954,34 +7167,34 @@
         <v>21</v>
       </c>
       <c r="AI14" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="AJ14" t="s">
         <v>176</v>
       </c>
       <c r="AL14" t="s">
-        <v>290</v>
+        <v>335</v>
       </c>
       <c r="AM14" t="s">
-        <v>300</v>
+        <v>355</v>
       </c>
       <c r="AN14" t="s">
-        <v>282</v>
+        <v>356</v>
       </c>
       <c r="AO14">
-        <v>0.99124474077666069</v>
+        <v>0.99874285064295787</v>
       </c>
       <c r="AP14">
-        <v>160.51308576122122</v>
+        <v>23.047738212439921</v>
       </c>
       <c r="AR14" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="AS14" t="s">
-        <v>309</v>
+        <v>372</v>
       </c>
       <c r="AT14" t="s">
-        <v>310</v>
+        <v>373</v>
       </c>
       <c r="AU14" t="s">
         <v>10</v>
@@ -6990,25 +7203,25 @@
         <v>21</v>
       </c>
       <c r="AW14" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="AX14" t="s">
         <v>176</v>
       </c>
       <c r="AZ14" t="s">
-        <v>309</v>
+        <v>372</v>
       </c>
       <c r="BA14" t="s">
-        <v>327</v>
+        <v>392</v>
       </c>
       <c r="BB14" t="s">
-        <v>328</v>
+        <v>393</v>
       </c>
       <c r="BC14">
-        <v>0.98349999607155203</v>
+        <v>0.98197790527844686</v>
       </c>
       <c r="BD14">
-        <v>302.50007202154563</v>
+        <v>330.40506989514142</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -7037,22 +7250,22 @@
         <v>183</v>
       </c>
       <c r="K15" t="s">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="L15">
-        <v>19.694351685424401</v>
+        <v>24.61852388350523</v>
       </c>
       <c r="M15">
-        <v>0.18112585613702831</v>
+        <v>0.1673342240929781</v>
       </c>
       <c r="O15" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="P15" t="s">
-        <v>242</v>
+        <v>263</v>
       </c>
       <c r="Q15" t="s">
-        <v>243</v>
+        <v>264</v>
       </c>
       <c r="R15" t="s">
         <v>10</v>
@@ -7061,37 +7274,37 @@
         <v>21</v>
       </c>
       <c r="T15" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="U15" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="V15" t="s">
         <v>176</v>
       </c>
       <c r="X15" t="s">
-        <v>242</v>
+        <v>263</v>
       </c>
       <c r="Y15" t="s">
         <v>228</v>
       </c>
       <c r="Z15" t="s">
-        <v>274</v>
+        <v>309</v>
       </c>
       <c r="AA15">
-        <v>0.99404697115518426</v>
+        <v>0.99800333095259353</v>
       </c>
       <c r="AB15">
-        <v>109.13886215495538</v>
+        <v>36.605599202451742</v>
       </c>
       <c r="AD15" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="AE15" t="s">
-        <v>292</v>
+        <v>337</v>
       </c>
       <c r="AF15" t="s">
-        <v>293</v>
+        <v>338</v>
       </c>
       <c r="AG15" t="s">
         <v>10</v>
@@ -7100,34 +7313,34 @@
         <v>21</v>
       </c>
       <c r="AI15" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="AJ15" t="s">
         <v>176</v>
       </c>
       <c r="AL15" t="s">
-        <v>292</v>
+        <v>337</v>
       </c>
       <c r="AM15" t="s">
-        <v>301</v>
+        <v>357</v>
       </c>
       <c r="AN15" t="s">
-        <v>297</v>
+        <v>328</v>
       </c>
       <c r="AO15">
-        <v>0.99439329011766553</v>
+        <v>0.99028422987608544</v>
       </c>
       <c r="AP15">
-        <v>102.78968117613158</v>
+        <v>178.1224522717672</v>
       </c>
       <c r="AR15" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="AS15" t="s">
-        <v>311</v>
+        <v>374</v>
       </c>
       <c r="AT15" t="s">
-        <v>312</v>
+        <v>375</v>
       </c>
       <c r="AU15" t="s">
         <v>10</v>
@@ -7136,25 +7349,25 @@
         <v>21</v>
       </c>
       <c r="AW15" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="AX15" t="s">
         <v>176</v>
       </c>
       <c r="AZ15" t="s">
-        <v>311</v>
+        <v>374</v>
       </c>
       <c r="BA15" t="s">
-        <v>329</v>
+        <v>394</v>
       </c>
       <c r="BB15" t="s">
-        <v>330</v>
+        <v>352</v>
       </c>
       <c r="BC15">
-        <v>0.9731327844491402</v>
+        <v>0.98911418404428342</v>
       </c>
       <c r="BD15">
-        <v>492.56561843243048</v>
+        <v>199.57329252147068</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -7183,22 +7396,22 @@
         <v>185</v>
       </c>
       <c r="K16" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="L16">
-        <v>24.89229309539002</v>
+        <v>30.989599999999999</v>
       </c>
       <c r="M16">
-        <v>0.17208130106952271</v>
+        <v>0.17299619696332699</v>
       </c>
       <c r="O16" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="P16" t="s">
-        <v>244</v>
+        <v>265</v>
       </c>
       <c r="Q16" t="s">
-        <v>245</v>
+        <v>266</v>
       </c>
       <c r="R16" t="s">
         <v>10</v>
@@ -7207,37 +7420,37 @@
         <v>21</v>
       </c>
       <c r="T16" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="U16" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="V16" t="s">
         <v>176</v>
       </c>
       <c r="X16" t="s">
+        <v>265</v>
+      </c>
+      <c r="Y16" t="s">
         <v>244</v>
       </c>
-      <c r="Y16" t="s">
-        <v>217</v>
-      </c>
       <c r="Z16" t="s">
-        <v>275</v>
+        <v>310</v>
       </c>
       <c r="AA16">
-        <v>0.99641029170642137</v>
+        <v>0.99842749356594429</v>
       </c>
       <c r="AB16">
-        <v>65.811318715607285</v>
+        <v>28.829284624355246</v>
       </c>
       <c r="AD16" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="AE16" t="s">
-        <v>294</v>
+        <v>339</v>
       </c>
       <c r="AF16" t="s">
-        <v>295</v>
+        <v>340</v>
       </c>
       <c r="AG16" t="s">
         <v>10</v>
@@ -7246,34 +7459,34 @@
         <v>21</v>
       </c>
       <c r="AI16" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="AJ16" t="s">
         <v>176</v>
       </c>
       <c r="AL16" t="s">
-        <v>294</v>
+        <v>339</v>
       </c>
       <c r="AM16" t="s">
-        <v>302</v>
+        <v>358</v>
       </c>
       <c r="AN16" t="s">
-        <v>282</v>
+        <v>350</v>
       </c>
       <c r="AO16">
-        <v>0.99023545286734149</v>
+        <v>0.99834719992221588</v>
       </c>
       <c r="AP16">
-        <v>179.01669743207171</v>
+        <v>30.301334759374811</v>
       </c>
       <c r="AR16" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="AS16" t="s">
-        <v>313</v>
+        <v>376</v>
       </c>
       <c r="AT16" t="s">
-        <v>314</v>
+        <v>377</v>
       </c>
       <c r="AU16" t="s">
         <v>10</v>
@@ -7282,25 +7495,25 @@
         <v>21</v>
       </c>
       <c r="AW16" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="AX16" t="s">
         <v>176</v>
       </c>
       <c r="AZ16" t="s">
-        <v>313</v>
+        <v>376</v>
       </c>
       <c r="BA16" t="s">
-        <v>331</v>
+        <v>395</v>
       </c>
       <c r="BB16" t="s">
-        <v>332</v>
+        <v>396</v>
       </c>
       <c r="BC16">
-        <v>0.98197790527844686</v>
+        <v>0.98500048755641589</v>
       </c>
       <c r="BD16">
-        <v>330.40506989514142</v>
+        <v>274.9910614657079</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -7329,22 +7542,22 @@
         <v>187</v>
       </c>
       <c r="K17" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="L17">
-        <v>17.849995582530354</v>
+        <v>9.1371868476021643</v>
       </c>
       <c r="M17">
-        <v>0.17108507887568539</v>
+        <v>0.19409506854904171</v>
       </c>
       <c r="O17" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="P17" t="s">
-        <v>246</v>
+        <v>267</v>
       </c>
       <c r="Q17" t="s">
-        <v>247</v>
+        <v>268</v>
       </c>
       <c r="R17" t="s">
         <v>10</v>
@@ -7353,37 +7566,73 @@
         <v>21</v>
       </c>
       <c r="T17" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="U17" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="V17" t="s">
         <v>176</v>
       </c>
       <c r="X17" t="s">
-        <v>246</v>
+        <v>267</v>
       </c>
       <c r="Y17" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="Z17" t="s">
-        <v>276</v>
+        <v>311</v>
       </c>
       <c r="AA17">
-        <v>0.99822394178768203</v>
+        <v>0.99575198492146944</v>
       </c>
       <c r="AB17">
-        <v>32.561067225829298</v>
+        <v>77.880276439726259</v>
+      </c>
+      <c r="AD17" t="s">
+        <v>252</v>
+      </c>
+      <c r="AE17" t="s">
+        <v>341</v>
+      </c>
+      <c r="AF17" t="s">
+        <v>342</v>
+      </c>
+      <c r="AG17" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH17" t="s">
+        <v>21</v>
+      </c>
+      <c r="AI17" t="s">
+        <v>256</v>
+      </c>
+      <c r="AJ17" t="s">
+        <v>176</v>
+      </c>
+      <c r="AL17" t="s">
+        <v>341</v>
+      </c>
+      <c r="AM17" t="s">
+        <v>359</v>
+      </c>
+      <c r="AN17" t="s">
+        <v>360</v>
+      </c>
+      <c r="AO17">
+        <v>0.99864191583933049</v>
+      </c>
+      <c r="AP17">
+        <v>24.898209612275185</v>
       </c>
       <c r="AR17" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="AS17" t="s">
-        <v>315</v>
+        <v>378</v>
       </c>
       <c r="AT17" t="s">
-        <v>316</v>
+        <v>379</v>
       </c>
       <c r="AU17" t="s">
         <v>10</v>
@@ -7392,25 +7641,25 @@
         <v>21</v>
       </c>
       <c r="AW17" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="AX17" t="s">
         <v>176</v>
       </c>
       <c r="AZ17" t="s">
-        <v>315</v>
+        <v>378</v>
       </c>
       <c r="BA17" t="s">
-        <v>333</v>
+        <v>397</v>
       </c>
       <c r="BB17" t="s">
-        <v>297</v>
+        <v>352</v>
       </c>
       <c r="BC17">
-        <v>0.98911418404428342</v>
+        <v>0.9926406959075802</v>
       </c>
       <c r="BD17">
-        <v>199.57329252147068</v>
+        <v>134.92057502769742</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -7439,22 +7688,22 @@
         <v>189</v>
       </c>
       <c r="K18" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="L18">
-        <v>8.2995000000000001</v>
+        <v>25.234798187507838</v>
       </c>
       <c r="M18">
-        <v>0.17416087148940759</v>
+        <v>0.18558087218738131</v>
       </c>
       <c r="O18" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="P18" t="s">
-        <v>248</v>
+        <v>269</v>
       </c>
       <c r="Q18" t="s">
-        <v>249</v>
+        <v>270</v>
       </c>
       <c r="R18" t="s">
         <v>10</v>
@@ -7463,37 +7712,73 @@
         <v>21</v>
       </c>
       <c r="T18" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="U18" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="V18" t="s">
         <v>176</v>
       </c>
       <c r="X18" t="s">
-        <v>248</v>
+        <v>269</v>
       </c>
       <c r="Y18" t="s">
-        <v>219</v>
+        <v>249</v>
       </c>
       <c r="Z18" t="s">
-        <v>277</v>
+        <v>312</v>
       </c>
       <c r="AA18">
-        <v>0.99742316095831862</v>
+        <v>0.99832626144038783</v>
       </c>
       <c r="AB18">
-        <v>47.242049097491972</v>
+        <v>30.685206926222389</v>
+      </c>
+      <c r="AD18" t="s">
+        <v>252</v>
+      </c>
+      <c r="AE18" t="s">
+        <v>343</v>
+      </c>
+      <c r="AF18" t="s">
+        <v>344</v>
+      </c>
+      <c r="AG18" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH18" t="s">
+        <v>21</v>
+      </c>
+      <c r="AI18" t="s">
+        <v>256</v>
+      </c>
+      <c r="AJ18" t="s">
+        <v>176</v>
+      </c>
+      <c r="AL18" t="s">
+        <v>343</v>
+      </c>
+      <c r="AM18" t="s">
+        <v>361</v>
+      </c>
+      <c r="AN18" t="s">
+        <v>362</v>
+      </c>
+      <c r="AO18">
+        <v>0.99774058703572632</v>
+      </c>
+      <c r="AP18">
+        <v>41.422571011684674</v>
       </c>
       <c r="AR18" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="AS18" t="s">
-        <v>317</v>
+        <v>380</v>
       </c>
       <c r="AT18" t="s">
-        <v>318</v>
+        <v>381</v>
       </c>
       <c r="AU18" t="s">
         <v>10</v>
@@ -7502,19 +7787,19 @@
         <v>21</v>
       </c>
       <c r="AW18" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="AX18" t="s">
         <v>176</v>
       </c>
       <c r="AZ18" t="s">
-        <v>317</v>
+        <v>380</v>
       </c>
       <c r="BA18" t="s">
-        <v>334</v>
+        <v>398</v>
       </c>
       <c r="BB18" t="s">
-        <v>335</v>
+        <v>399</v>
       </c>
       <c r="BC18">
         <v>0.97644633349267118</v>
@@ -7549,22 +7834,22 @@
         <v>191</v>
       </c>
       <c r="K19" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="L19">
-        <v>19.930590447679613</v>
+        <v>6.8944010734263976</v>
       </c>
       <c r="M19">
-        <v>0.16679423361779411</v>
+        <v>0.1688408594584874</v>
       </c>
       <c r="O19" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="P19" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="Q19" t="s">
-        <v>251</v>
+        <v>272</v>
       </c>
       <c r="R19" t="s">
         <v>10</v>
@@ -7573,37 +7858,73 @@
         <v>21</v>
       </c>
       <c r="T19" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="U19" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="V19" t="s">
         <v>176</v>
       </c>
       <c r="X19" t="s">
+        <v>271</v>
+      </c>
+      <c r="Y19" t="s">
         <v>250</v>
       </c>
-      <c r="Y19" t="s">
-        <v>223</v>
-      </c>
       <c r="Z19" t="s">
-        <v>278</v>
+        <v>313</v>
       </c>
       <c r="AA19">
-        <v>0.99833039272231761</v>
+        <v>0.99807075307977899</v>
       </c>
       <c r="AB19">
-        <v>30.609466757511377</v>
+        <v>35.369526870718673</v>
+      </c>
+      <c r="AD19" t="s">
+        <v>252</v>
+      </c>
+      <c r="AE19" t="s">
+        <v>345</v>
+      </c>
+      <c r="AF19" t="s">
+        <v>346</v>
+      </c>
+      <c r="AG19" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH19" t="s">
+        <v>21</v>
+      </c>
+      <c r="AI19" t="s">
+        <v>256</v>
+      </c>
+      <c r="AJ19" t="s">
+        <v>176</v>
+      </c>
+      <c r="AL19" t="s">
+        <v>345</v>
+      </c>
+      <c r="AM19" t="s">
+        <v>363</v>
+      </c>
+      <c r="AN19" t="s">
+        <v>364</v>
+      </c>
+      <c r="AO19">
+        <v>0.99280840617902688</v>
+      </c>
+      <c r="AP19">
+        <v>131.84588671784124</v>
       </c>
       <c r="AR19" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="AS19" t="s">
-        <v>319</v>
+        <v>382</v>
       </c>
       <c r="AT19" t="s">
-        <v>320</v>
+        <v>383</v>
       </c>
       <c r="AU19" t="s">
         <v>10</v>
@@ -7612,19 +7933,19 @@
         <v>21</v>
       </c>
       <c r="AW19" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="AX19" t="s">
         <v>176</v>
       </c>
       <c r="AZ19" t="s">
-        <v>319</v>
+        <v>382</v>
       </c>
       <c r="BA19" t="s">
-        <v>336</v>
+        <v>400</v>
       </c>
       <c r="BB19" t="s">
-        <v>297</v>
+        <v>352</v>
       </c>
       <c r="BC19">
         <v>0.98985596153199862</v>
@@ -7659,22 +7980,22 @@
         <v>193</v>
       </c>
       <c r="K20" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="L20">
-        <v>24.464593112389704</v>
+        <v>3.5395407988285168</v>
       </c>
       <c r="M20">
-        <v>0.17332124852788691</v>
+        <v>0.16836736993763851</v>
       </c>
       <c r="O20" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="P20" t="s">
-        <v>252</v>
+        <v>273</v>
       </c>
       <c r="Q20" t="s">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="R20" t="s">
         <v>10</v>
@@ -7683,37 +8004,73 @@
         <v>21</v>
       </c>
       <c r="T20" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="U20" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="V20" t="s">
         <v>176</v>
       </c>
       <c r="X20" t="s">
+        <v>273</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>232</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>314</v>
+      </c>
+      <c r="AA20">
+        <v>0.99810016004702629</v>
+      </c>
+      <c r="AB20">
+        <v>34.830399137852275</v>
+      </c>
+      <c r="AD20" t="s">
         <v>252</v>
       </c>
-      <c r="Y20" t="s">
-        <v>216</v>
-      </c>
-      <c r="Z20" t="s">
-        <v>279</v>
-      </c>
-      <c r="AA20">
-        <v>0.99124301005043802</v>
-      </c>
-      <c r="AB20">
-        <v>160.54481574197013</v>
+      <c r="AE20" t="s">
+        <v>347</v>
+      </c>
+      <c r="AF20" t="s">
+        <v>348</v>
+      </c>
+      <c r="AG20" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH20" t="s">
+        <v>21</v>
+      </c>
+      <c r="AI20" t="s">
+        <v>256</v>
+      </c>
+      <c r="AJ20" t="s">
+        <v>176</v>
+      </c>
+      <c r="AL20" t="s">
+        <v>347</v>
+      </c>
+      <c r="AM20" t="s">
+        <v>365</v>
+      </c>
+      <c r="AN20" t="s">
+        <v>352</v>
+      </c>
+      <c r="AO20">
+        <v>0.99351413211341089</v>
+      </c>
+      <c r="AP20">
+        <v>118.90757792080102</v>
       </c>
       <c r="AR20" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="AS20" t="s">
-        <v>321</v>
+        <v>384</v>
       </c>
       <c r="AT20" t="s">
-        <v>322</v>
+        <v>385</v>
       </c>
       <c r="AU20" t="s">
         <v>10</v>
@@ -7722,25 +8079,25 @@
         <v>21</v>
       </c>
       <c r="AW20" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="AX20" t="s">
         <v>176</v>
       </c>
       <c r="AZ20" t="s">
-        <v>321</v>
+        <v>384</v>
       </c>
       <c r="BA20" t="s">
-        <v>337</v>
+        <v>401</v>
       </c>
       <c r="BB20" t="s">
-        <v>338</v>
+        <v>352</v>
       </c>
       <c r="BC20">
-        <v>0.98322281233462283</v>
+        <v>0.98051979717181825</v>
       </c>
       <c r="BD20">
-        <v>307.58177386524892</v>
+        <v>357.13705184999884</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -7769,52 +8126,52 @@
         <v>195</v>
       </c>
       <c r="K21" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="L21">
-        <v>9.1371868476021643</v>
+        <v>7.2319154710702218</v>
       </c>
       <c r="M21">
-        <v>0.19409506854904171</v>
+        <v>0.1751515882634313</v>
       </c>
       <c r="O21" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="P21" t="s">
-        <v>254</v>
+        <v>275</v>
       </c>
       <c r="Q21" t="s">
+        <v>276</v>
+      </c>
+      <c r="R21" t="s">
+        <v>10</v>
+      </c>
+      <c r="S21" t="s">
+        <v>21</v>
+      </c>
+      <c r="T21" t="s">
         <v>255</v>
       </c>
-      <c r="R21" t="s">
-        <v>10</v>
-      </c>
-      <c r="S21" t="s">
-        <v>21</v>
-      </c>
-      <c r="T21" t="s">
-        <v>234</v>
-      </c>
       <c r="U21" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="V21" t="s">
         <v>176</v>
       </c>
       <c r="X21" t="s">
-        <v>254</v>
+        <v>275</v>
       </c>
       <c r="Y21" t="s">
-        <v>215</v>
+        <v>248</v>
       </c>
       <c r="Z21" t="s">
-        <v>275</v>
+        <v>315</v>
       </c>
       <c r="AA21">
-        <v>0.99290727743954299</v>
+        <v>0.99824011961767123</v>
       </c>
       <c r="AB21">
-        <v>130.03324694171172</v>
+        <v>32.264473676027947</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -7843,52 +8200,52 @@
         <v>197</v>
       </c>
       <c r="K22" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="L22">
-        <v>15.348103461071128</v>
+        <v>17.875390154313386</v>
       </c>
       <c r="M22">
-        <v>0.18532431943075209</v>
+        <v>0.18432712863461151</v>
       </c>
       <c r="O22" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="P22" t="s">
+        <v>277</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>278</v>
+      </c>
+      <c r="R22" t="s">
+        <v>10</v>
+      </c>
+      <c r="S22" t="s">
+        <v>21</v>
+      </c>
+      <c r="T22" t="s">
+        <v>255</v>
+      </c>
+      <c r="U22" t="s">
         <v>256</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>257</v>
-      </c>
-      <c r="R22" t="s">
-        <v>10</v>
-      </c>
-      <c r="S22" t="s">
-        <v>21</v>
-      </c>
-      <c r="T22" t="s">
-        <v>234</v>
-      </c>
-      <c r="U22" t="s">
-        <v>235</v>
       </c>
       <c r="V22" t="s">
         <v>176</v>
       </c>
       <c r="X22" t="s">
-        <v>256</v>
+        <v>277</v>
       </c>
       <c r="Y22" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="Z22" t="s">
-        <v>280</v>
+        <v>316</v>
       </c>
       <c r="AA22">
-        <v>0.99792831960738038</v>
+        <v>0.99638966070385804</v>
       </c>
       <c r="AB22">
-        <v>37.980807198026596</v>
+        <v>66.189553762601733</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -7917,22 +8274,22 @@
         <v>199</v>
       </c>
       <c r="K23" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="L23">
-        <v>6.8944010734263976</v>
+        <v>18.06083474528435</v>
       </c>
       <c r="M23">
-        <v>0.1688408594584874</v>
+        <v>0.17094151717874401</v>
       </c>
       <c r="O23" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="P23" t="s">
-        <v>258</v>
+        <v>279</v>
       </c>
       <c r="Q23" t="s">
-        <v>259</v>
+        <v>280</v>
       </c>
       <c r="R23" t="s">
         <v>10</v>
@@ -7941,28 +8298,28 @@
         <v>21</v>
       </c>
       <c r="T23" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="U23" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="V23" t="s">
         <v>176</v>
       </c>
       <c r="X23" t="s">
-        <v>258</v>
+        <v>279</v>
       </c>
       <c r="Y23" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="Z23" t="s">
-        <v>281</v>
+        <v>317</v>
       </c>
       <c r="AA23">
-        <v>0.9940167733084464</v>
+        <v>0.99742391546858211</v>
       </c>
       <c r="AB23">
-        <v>109.69248934514933</v>
+        <v>47.228216409328219</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -7991,22 +8348,22 @@
         <v>201</v>
       </c>
       <c r="K24" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="L24">
-        <v>2.9785407988285173</v>
+        <v>28.405993716121667</v>
       </c>
       <c r="M24">
-        <v>0.16826277378901389</v>
+        <v>0.1865975423692938</v>
       </c>
       <c r="O24" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="P24" t="s">
-        <v>260</v>
+        <v>281</v>
       </c>
       <c r="Q24" t="s">
-        <v>261</v>
+        <v>282</v>
       </c>
       <c r="R24" t="s">
         <v>10</v>
@@ -8015,28 +8372,28 @@
         <v>21</v>
       </c>
       <c r="T24" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="U24" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="V24" t="s">
         <v>176</v>
       </c>
       <c r="X24" t="s">
-        <v>260</v>
+        <v>281</v>
       </c>
       <c r="Y24" t="s">
-        <v>213</v>
+        <v>241</v>
       </c>
       <c r="Z24" t="s">
-        <v>282</v>
+        <v>318</v>
       </c>
       <c r="AA24">
-        <v>0.99541857140439349</v>
+        <v>0.9926616850494836</v>
       </c>
       <c r="AB24">
-        <v>83.992857586119158</v>
+        <v>134.53577409280112</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -8065,22 +8422,22 @@
         <v>203</v>
       </c>
       <c r="K25" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="L25">
-        <v>28.364140154313386</v>
+        <v>7.7286013946838557</v>
       </c>
       <c r="M25">
-        <v>0.18480604258021721</v>
+        <v>0.1775891198754492</v>
       </c>
       <c r="O25" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="P25" t="s">
-        <v>262</v>
+        <v>283</v>
       </c>
       <c r="Q25" t="s">
-        <v>263</v>
+        <v>284</v>
       </c>
       <c r="R25" t="s">
         <v>10</v>
@@ -8089,28 +8446,28 @@
         <v>21</v>
       </c>
       <c r="T25" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="U25" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="V25" t="s">
         <v>176</v>
       </c>
       <c r="X25" t="s">
-        <v>262</v>
+        <v>283</v>
       </c>
       <c r="Y25" t="s">
-        <v>214</v>
+        <v>246</v>
       </c>
       <c r="Z25" t="s">
-        <v>282</v>
+        <v>319</v>
       </c>
       <c r="AA25">
-        <v>0.99301257726365455</v>
+        <v>0.99865070901751662</v>
       </c>
       <c r="AB25">
-        <v>128.1027501663325</v>
+        <v>24.737001345528363</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -8139,22 +8496,22 @@
         <v>205</v>
       </c>
       <c r="K26" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="L26">
-        <v>3.3216101975069243</v>
+        <v>28.78591875420447</v>
       </c>
       <c r="M26">
-        <v>0.17205268996729081</v>
+        <v>0.1872387521975411</v>
       </c>
       <c r="O26" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="P26" t="s">
-        <v>264</v>
+        <v>285</v>
       </c>
       <c r="Q26" t="s">
-        <v>265</v>
+        <v>286</v>
       </c>
       <c r="R26" t="s">
         <v>10</v>
@@ -8163,28 +8520,28 @@
         <v>21</v>
       </c>
       <c r="T26" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="U26" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="V26" t="s">
         <v>176</v>
       </c>
       <c r="X26" t="s">
-        <v>264</v>
+        <v>285</v>
       </c>
       <c r="Y26" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="Z26" t="s">
-        <v>283</v>
+        <v>320</v>
       </c>
       <c r="AA26">
-        <v>0.9970455298234584</v>
+        <v>0.99858590981741613</v>
       </c>
       <c r="AB26">
-        <v>54.165286569929123</v>
+        <v>25.924986680704325</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -8213,22 +8570,22 @@
         <v>207</v>
       </c>
       <c r="K27" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="L27">
-        <v>10.861791649894323</v>
+        <v>14.623449250357137</v>
       </c>
       <c r="M27">
-        <v>0.1718933316059254</v>
+        <v>0.18557709573079659</v>
       </c>
       <c r="O27" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="P27" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="Q27" t="s">
-        <v>267</v>
+        <v>288</v>
       </c>
       <c r="R27" t="s">
         <v>10</v>
@@ -8237,28 +8594,546 @@
         <v>21</v>
       </c>
       <c r="T27" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="U27" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="V27" t="s">
         <v>176</v>
       </c>
       <c r="X27" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="Y27" t="s">
-        <v>226</v>
+        <v>245</v>
       </c>
       <c r="Z27" t="s">
-        <v>274</v>
+        <v>321</v>
       </c>
       <c r="AA27">
-        <v>0.99388261520871601</v>
+        <v>0.99800942183417862</v>
       </c>
       <c r="AB27">
-        <v>112.15205450687272</v>
+        <v>36.493933040058664</v>
+      </c>
+    </row>
+    <row r="28" spans="2:56">
+      <c r="B28" t="s">
+        <v>172</v>
+      </c>
+      <c r="C28" t="s">
+        <v>209</v>
+      </c>
+      <c r="D28" t="s">
+        <v>210</v>
+      </c>
+      <c r="E28" t="s">
+        <v>10</v>
+      </c>
+      <c r="F28" t="s">
+        <v>21</v>
+      </c>
+      <c r="G28" t="s">
+        <v>175</v>
+      </c>
+      <c r="H28" t="s">
+        <v>176</v>
+      </c>
+      <c r="J28" t="s">
+        <v>209</v>
+      </c>
+      <c r="K28" t="s">
+        <v>244</v>
+      </c>
+      <c r="L28">
+        <v>15.857550133529749</v>
+      </c>
+      <c r="M28">
+        <v>0.1803561915746198</v>
+      </c>
+      <c r="O28" t="s">
+        <v>252</v>
+      </c>
+      <c r="P28" t="s">
+        <v>289</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>290</v>
+      </c>
+      <c r="R28" t="s">
+        <v>10</v>
+      </c>
+      <c r="S28" t="s">
+        <v>21</v>
+      </c>
+      <c r="T28" t="s">
+        <v>255</v>
+      </c>
+      <c r="U28" t="s">
+        <v>256</v>
+      </c>
+      <c r="V28" t="s">
+        <v>176</v>
+      </c>
+      <c r="X28" t="s">
+        <v>289</v>
+      </c>
+      <c r="Y28" t="s">
+        <v>236</v>
+      </c>
+      <c r="Z28" t="s">
+        <v>322</v>
+      </c>
+      <c r="AA28">
+        <v>0.99467655833764279</v>
+      </c>
+      <c r="AB28">
+        <v>97.596430476549543</v>
+      </c>
+    </row>
+    <row r="29" spans="2:56">
+      <c r="B29" t="s">
+        <v>172</v>
+      </c>
+      <c r="C29" t="s">
+        <v>211</v>
+      </c>
+      <c r="D29" t="s">
+        <v>212</v>
+      </c>
+      <c r="E29" t="s">
+        <v>10</v>
+      </c>
+      <c r="F29" t="s">
+        <v>21</v>
+      </c>
+      <c r="G29" t="s">
+        <v>175</v>
+      </c>
+      <c r="H29" t="s">
+        <v>176</v>
+      </c>
+      <c r="J29" t="s">
+        <v>211</v>
+      </c>
+      <c r="K29" t="s">
+        <v>245</v>
+      </c>
+      <c r="L29">
+        <v>32.737700060872804</v>
+      </c>
+      <c r="M29">
+        <v>0.17705805581656009</v>
+      </c>
+      <c r="O29" t="s">
+        <v>252</v>
+      </c>
+      <c r="P29" t="s">
+        <v>291</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>292</v>
+      </c>
+      <c r="R29" t="s">
+        <v>10</v>
+      </c>
+      <c r="S29" t="s">
+        <v>21</v>
+      </c>
+      <c r="T29" t="s">
+        <v>255</v>
+      </c>
+      <c r="U29" t="s">
+        <v>256</v>
+      </c>
+      <c r="V29" t="s">
+        <v>176</v>
+      </c>
+      <c r="X29" t="s">
+        <v>291</v>
+      </c>
+      <c r="Y29" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z29" t="s">
+        <v>323</v>
+      </c>
+      <c r="AA29">
+        <v>0.99689028832030402</v>
+      </c>
+      <c r="AB29">
+        <v>57.011380794425911</v>
+      </c>
+    </row>
+    <row r="30" spans="2:56">
+      <c r="B30" t="s">
+        <v>172</v>
+      </c>
+      <c r="C30" t="s">
+        <v>213</v>
+      </c>
+      <c r="D30" t="s">
+        <v>214</v>
+      </c>
+      <c r="E30" t="s">
+        <v>10</v>
+      </c>
+      <c r="F30" t="s">
+        <v>21</v>
+      </c>
+      <c r="G30" t="s">
+        <v>175</v>
+      </c>
+      <c r="H30" t="s">
+        <v>176</v>
+      </c>
+      <c r="J30" t="s">
+        <v>213</v>
+      </c>
+      <c r="K30" t="s">
+        <v>246</v>
+      </c>
+      <c r="L30">
+        <v>26.809027827217307</v>
+      </c>
+      <c r="M30">
+        <v>0.18079715434538041</v>
+      </c>
+      <c r="O30" t="s">
+        <v>252</v>
+      </c>
+      <c r="P30" t="s">
+        <v>293</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>294</v>
+      </c>
+      <c r="R30" t="s">
+        <v>10</v>
+      </c>
+      <c r="S30" t="s">
+        <v>21</v>
+      </c>
+      <c r="T30" t="s">
+        <v>255</v>
+      </c>
+      <c r="U30" t="s">
+        <v>256</v>
+      </c>
+      <c r="V30" t="s">
+        <v>176</v>
+      </c>
+      <c r="X30" t="s">
+        <v>293</v>
+      </c>
+      <c r="Y30" t="s">
+        <v>233</v>
+      </c>
+      <c r="Z30" t="s">
+        <v>324</v>
+      </c>
+      <c r="AA30">
+        <v>0.99833039272231761</v>
+      </c>
+      <c r="AB30">
+        <v>30.609466757511377</v>
+      </c>
+    </row>
+    <row r="31" spans="2:56">
+      <c r="B31" t="s">
+        <v>172</v>
+      </c>
+      <c r="C31" t="s">
+        <v>215</v>
+      </c>
+      <c r="D31" t="s">
+        <v>216</v>
+      </c>
+      <c r="E31" t="s">
+        <v>10</v>
+      </c>
+      <c r="F31" t="s">
+        <v>21</v>
+      </c>
+      <c r="G31" t="s">
+        <v>175</v>
+      </c>
+      <c r="H31" t="s">
+        <v>176</v>
+      </c>
+      <c r="J31" t="s">
+        <v>215</v>
+      </c>
+      <c r="K31" t="s">
+        <v>247</v>
+      </c>
+      <c r="L31">
+        <v>13.739734552558454</v>
+      </c>
+      <c r="M31">
+        <v>0.16946732323393451</v>
+      </c>
+      <c r="O31" t="s">
+        <v>252</v>
+      </c>
+      <c r="P31" t="s">
+        <v>295</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>296</v>
+      </c>
+      <c r="R31" t="s">
+        <v>10</v>
+      </c>
+      <c r="S31" t="s">
+        <v>21</v>
+      </c>
+      <c r="T31" t="s">
+        <v>255</v>
+      </c>
+      <c r="U31" t="s">
+        <v>256</v>
+      </c>
+      <c r="V31" t="s">
+        <v>176</v>
+      </c>
+      <c r="X31" t="s">
+        <v>295</v>
+      </c>
+      <c r="Y31" t="s">
+        <v>238</v>
+      </c>
+      <c r="Z31" t="s">
+        <v>325</v>
+      </c>
+      <c r="AA31">
+        <v>0.99852761354689235</v>
+      </c>
+      <c r="AB31">
+        <v>26.993751640306677</v>
+      </c>
+    </row>
+    <row r="32" spans="2:56">
+      <c r="B32" t="s">
+        <v>172</v>
+      </c>
+      <c r="C32" t="s">
+        <v>217</v>
+      </c>
+      <c r="D32" t="s">
+        <v>218</v>
+      </c>
+      <c r="E32" t="s">
+        <v>10</v>
+      </c>
+      <c r="F32" t="s">
+        <v>21</v>
+      </c>
+      <c r="G32" t="s">
+        <v>175</v>
+      </c>
+      <c r="H32" t="s">
+        <v>176</v>
+      </c>
+      <c r="J32" t="s">
+        <v>217</v>
+      </c>
+      <c r="K32" t="s">
+        <v>248</v>
+      </c>
+      <c r="L32">
+        <v>18.266099309667155</v>
+      </c>
+      <c r="M32">
+        <v>0.1767783425893853</v>
+      </c>
+      <c r="O32" t="s">
+        <v>252</v>
+      </c>
+      <c r="P32" t="s">
+        <v>297</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>298</v>
+      </c>
+      <c r="R32" t="s">
+        <v>10</v>
+      </c>
+      <c r="S32" t="s">
+        <v>21</v>
+      </c>
+      <c r="T32" t="s">
+        <v>255</v>
+      </c>
+      <c r="U32" t="s">
+        <v>256</v>
+      </c>
+      <c r="V32" t="s">
+        <v>176</v>
+      </c>
+      <c r="X32" t="s">
+        <v>297</v>
+      </c>
+      <c r="Y32" t="s">
+        <v>234</v>
+      </c>
+      <c r="Z32" t="s">
+        <v>326</v>
+      </c>
+      <c r="AA32">
+        <v>0.99619128062121887</v>
+      </c>
+      <c r="AB32">
+        <v>69.826521944320177</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28">
+      <c r="B33" t="s">
+        <v>172</v>
+      </c>
+      <c r="C33" t="s">
+        <v>219</v>
+      </c>
+      <c r="D33" t="s">
+        <v>220</v>
+      </c>
+      <c r="E33" t="s">
+        <v>10</v>
+      </c>
+      <c r="F33" t="s">
+        <v>21</v>
+      </c>
+      <c r="G33" t="s">
+        <v>175</v>
+      </c>
+      <c r="H33" t="s">
+        <v>176</v>
+      </c>
+      <c r="J33" t="s">
+        <v>219</v>
+      </c>
+      <c r="K33" t="s">
+        <v>249</v>
+      </c>
+      <c r="L33">
+        <v>4.3084406521767775</v>
+      </c>
+      <c r="M33">
+        <v>0.18312711409436019</v>
+      </c>
+      <c r="O33" t="s">
+        <v>252</v>
+      </c>
+      <c r="P33" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>300</v>
+      </c>
+      <c r="R33" t="s">
+        <v>10</v>
+      </c>
+      <c r="S33" t="s">
+        <v>21</v>
+      </c>
+      <c r="T33" t="s">
+        <v>255</v>
+      </c>
+      <c r="U33" t="s">
+        <v>256</v>
+      </c>
+      <c r="V33" t="s">
+        <v>176</v>
+      </c>
+      <c r="X33" t="s">
+        <v>299</v>
+      </c>
+      <c r="Y33" t="s">
+        <v>235</v>
+      </c>
+      <c r="Z33" t="s">
+        <v>327</v>
+      </c>
+      <c r="AA33">
+        <v>0.9940167733084464</v>
+      </c>
+      <c r="AB33">
+        <v>109.69248934514933</v>
+      </c>
+    </row>
+    <row r="34" spans="2:28">
+      <c r="B34" t="s">
+        <v>172</v>
+      </c>
+      <c r="C34" t="s">
+        <v>221</v>
+      </c>
+      <c r="D34" t="s">
+        <v>222</v>
+      </c>
+      <c r="E34" t="s">
+        <v>10</v>
+      </c>
+      <c r="F34" t="s">
+        <v>21</v>
+      </c>
+      <c r="G34" t="s">
+        <v>175</v>
+      </c>
+      <c r="H34" t="s">
+        <v>176</v>
+      </c>
+      <c r="J34" t="s">
+        <v>221</v>
+      </c>
+      <c r="K34" t="s">
+        <v>250</v>
+      </c>
+      <c r="L34">
+        <v>26.330312143220432</v>
+      </c>
+      <c r="M34">
+        <v>0.18881758058774631</v>
+      </c>
+      <c r="O34" t="s">
+        <v>252</v>
+      </c>
+      <c r="P34" t="s">
+        <v>301</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>302</v>
+      </c>
+      <c r="R34" t="s">
+        <v>10</v>
+      </c>
+      <c r="S34" t="s">
+        <v>21</v>
+      </c>
+      <c r="T34" t="s">
+        <v>255</v>
+      </c>
+      <c r="U34" t="s">
+        <v>256</v>
+      </c>
+      <c r="V34" t="s">
+        <v>176</v>
+      </c>
+      <c r="X34" t="s">
+        <v>301</v>
+      </c>
+      <c r="Y34" t="s">
+        <v>240</v>
+      </c>
+      <c r="Z34" t="s">
+        <v>328</v>
+      </c>
+      <c r="AA34">
+        <v>0.99314588501373713</v>
+      </c>
+      <c r="AB34">
+        <v>125.65877474815255</v>
       </c>
     </row>
   </sheetData>
@@ -8267,7 +9142,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B83D7E3-5C4E-494E-9B6B-308BC488DCE8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33422FC4-D2BD-47C1-BCE8-F067F32EF243}">
   <dimension ref="B9:Z20"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -8276,13 +9151,13 @@
         <v>164</v>
       </c>
       <c r="J9" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="O9" t="s">
         <v>164</v>
       </c>
       <c r="W9" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
     </row>
     <row r="10" spans="2:26">
@@ -8311,13 +9186,13 @@
         <v>166</v>
       </c>
       <c r="K10" t="s">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="L10" t="s">
-        <v>211</v>
+        <v>225</v>
       </c>
       <c r="M10" t="s">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="O10" t="s">
         <v>165</v>
@@ -8344,13 +9219,13 @@
         <v>166</v>
       </c>
       <c r="X10" t="s">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="Y10" t="s">
-        <v>211</v>
+        <v>225</v>
       </c>
       <c r="Z10" t="s">
-        <v>212</v>
+        <v>226</v>
       </c>
     </row>
     <row r="11" spans="2:26">
@@ -8358,10 +9233,10 @@
         <v>172</v>
       </c>
       <c r="C11" t="s">
-        <v>339</v>
+        <v>402</v>
       </c>
       <c r="D11" t="s">
-        <v>340</v>
+        <v>403</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
@@ -8376,25 +9251,25 @@
         <v>176</v>
       </c>
       <c r="J11" t="s">
-        <v>339</v>
+        <v>402</v>
       </c>
       <c r="K11" t="s">
-        <v>298</v>
+        <v>357</v>
       </c>
       <c r="L11">
-        <v>5.3956320681287483E-3</v>
+        <v>0.23246532253847452</v>
       </c>
       <c r="M11">
-        <v>0.1254362290471146</v>
+        <v>0.17134845118368069</v>
       </c>
       <c r="O11" t="s">
         <v>172</v>
       </c>
       <c r="P11" t="s">
-        <v>351</v>
+        <v>422</v>
       </c>
       <c r="Q11" t="s">
-        <v>352</v>
+        <v>423</v>
       </c>
       <c r="R11" t="s">
         <v>10</v>
@@ -8409,10 +9284,10 @@
         <v>176</v>
       </c>
       <c r="W11" t="s">
-        <v>351</v>
+        <v>422</v>
       </c>
       <c r="X11" t="s">
-        <v>329</v>
+        <v>390</v>
       </c>
       <c r="Y11">
         <v>1.9035</v>
@@ -8426,10 +9301,10 @@
         <v>172</v>
       </c>
       <c r="C12" t="s">
-        <v>341</v>
+        <v>404</v>
       </c>
       <c r="D12" t="s">
-        <v>342</v>
+        <v>405</v>
       </c>
       <c r="E12" t="s">
         <v>10</v>
@@ -8444,25 +9319,25 @@
         <v>176</v>
       </c>
       <c r="J12" t="s">
-        <v>341</v>
+        <v>404</v>
       </c>
       <c r="K12" t="s">
-        <v>296</v>
+        <v>351</v>
       </c>
       <c r="L12">
-        <v>3.4940612871927561E-2</v>
+        <v>4.0336244940056304E-2</v>
       </c>
       <c r="M12">
-        <v>0.17102414841071339</v>
+        <v>0.1649260190483236</v>
       </c>
       <c r="O12" t="s">
         <v>172</v>
       </c>
       <c r="P12" t="s">
-        <v>353</v>
+        <v>424</v>
       </c>
       <c r="Q12" t="s">
-        <v>354</v>
+        <v>425</v>
       </c>
       <c r="R12" t="s">
         <v>10</v>
@@ -8477,10 +9352,10 @@
         <v>176</v>
       </c>
       <c r="W12" t="s">
-        <v>353</v>
+        <v>424</v>
       </c>
       <c r="X12" t="s">
-        <v>324</v>
+        <v>395</v>
       </c>
       <c r="Y12">
         <v>1.0927500000000001</v>
@@ -8494,10 +9369,10 @@
         <v>172</v>
       </c>
       <c r="C13" t="s">
-        <v>343</v>
+        <v>406</v>
       </c>
       <c r="D13" t="s">
-        <v>344</v>
+        <v>407</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
@@ -8512,25 +9387,25 @@
         <v>176</v>
       </c>
       <c r="J13" t="s">
-        <v>343</v>
+        <v>406</v>
       </c>
       <c r="K13" t="s">
-        <v>301</v>
+        <v>365</v>
       </c>
       <c r="L13">
-        <v>0.55387242169595108</v>
+        <v>0.84033275315984202</v>
       </c>
       <c r="M13">
-        <v>8.2892322775308197E-2</v>
+        <v>0.1303096753009709</v>
       </c>
       <c r="O13" t="s">
         <v>172</v>
       </c>
       <c r="P13" t="s">
-        <v>355</v>
+        <v>426</v>
       </c>
       <c r="Q13" t="s">
-        <v>356</v>
+        <v>427</v>
       </c>
       <c r="R13" t="s">
         <v>10</v>
@@ -8545,10 +9420,10 @@
         <v>176</v>
       </c>
       <c r="W13" t="s">
-        <v>355</v>
+        <v>426</v>
       </c>
       <c r="X13" t="s">
-        <v>327</v>
+        <v>388</v>
       </c>
       <c r="Y13">
         <v>3.08175</v>
@@ -8562,10 +9437,10 @@
         <v>172</v>
       </c>
       <c r="C14" t="s">
-        <v>345</v>
+        <v>408</v>
       </c>
       <c r="D14" t="s">
-        <v>346</v>
+        <v>409</v>
       </c>
       <c r="E14" t="s">
         <v>10</v>
@@ -8580,25 +9455,25 @@
         <v>176</v>
       </c>
       <c r="J14" t="s">
-        <v>345</v>
+        <v>408</v>
       </c>
       <c r="K14" t="s">
-        <v>299</v>
+        <v>361</v>
       </c>
       <c r="L14">
-        <v>0.28646033146389088</v>
+        <v>1.0872903918273968</v>
       </c>
       <c r="M14">
-        <v>0.22199135331756539</v>
+        <v>9.8657259505711498E-2</v>
       </c>
       <c r="O14" t="s">
         <v>172</v>
       </c>
       <c r="P14" t="s">
-        <v>357</v>
+        <v>428</v>
       </c>
       <c r="Q14" t="s">
-        <v>358</v>
+        <v>429</v>
       </c>
       <c r="R14" t="s">
         <v>10</v>
@@ -8613,10 +9488,10 @@
         <v>176</v>
       </c>
       <c r="W14" t="s">
-        <v>357</v>
+        <v>428</v>
       </c>
       <c r="X14" t="s">
-        <v>326</v>
+        <v>397</v>
       </c>
       <c r="Y14">
         <v>7.6124999999999998</v>
@@ -8630,10 +9505,10 @@
         <v>172</v>
       </c>
       <c r="C15" t="s">
-        <v>347</v>
+        <v>410</v>
       </c>
       <c r="D15" t="s">
-        <v>348</v>
+        <v>411</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
@@ -8648,25 +9523,25 @@
         <v>176</v>
       </c>
       <c r="J15" t="s">
-        <v>347</v>
+        <v>410</v>
       </c>
       <c r="K15" t="s">
-        <v>302</v>
+        <v>359</v>
       </c>
       <c r="L15">
-        <v>0.22123070557198549</v>
+        <v>0.41379018787058752</v>
       </c>
       <c r="M15">
-        <v>0.17157806530573419</v>
+        <v>9.3893742969819796E-2</v>
       </c>
       <c r="O15" t="s">
         <v>172</v>
       </c>
       <c r="P15" t="s">
-        <v>359</v>
+        <v>430</v>
       </c>
       <c r="Q15" t="s">
-        <v>360</v>
+        <v>431</v>
       </c>
       <c r="R15" t="s">
         <v>10</v>
@@ -8681,10 +9556,10 @@
         <v>176</v>
       </c>
       <c r="W15" t="s">
-        <v>359</v>
+        <v>430</v>
       </c>
       <c r="X15" t="s">
-        <v>333</v>
+        <v>394</v>
       </c>
       <c r="Y15">
         <v>7.6687500000000002</v>
@@ -8698,10 +9573,10 @@
         <v>172</v>
       </c>
       <c r="C16" t="s">
-        <v>349</v>
+        <v>412</v>
       </c>
       <c r="D16" t="s">
-        <v>350</v>
+        <v>413</v>
       </c>
       <c r="E16" t="s">
         <v>10</v>
@@ -8716,25 +9591,25 @@
         <v>176</v>
       </c>
       <c r="J16" t="s">
-        <v>349</v>
+        <v>412</v>
       </c>
       <c r="K16" t="s">
-        <v>300</v>
+        <v>358</v>
       </c>
       <c r="L16">
-        <v>1.1234616966489041E-2</v>
+        <v>0.22566824167830141</v>
       </c>
       <c r="M16">
-        <v>0.1668269179277872</v>
+        <v>9.7340783555856694E-2</v>
       </c>
       <c r="O16" t="s">
         <v>172</v>
       </c>
       <c r="P16" t="s">
-        <v>361</v>
+        <v>432</v>
       </c>
       <c r="Q16" t="s">
-        <v>362</v>
+        <v>433</v>
       </c>
       <c r="R16" t="s">
         <v>10</v>
@@ -8749,10 +9624,10 @@
         <v>176</v>
       </c>
       <c r="W16" t="s">
-        <v>361</v>
+        <v>432</v>
       </c>
       <c r="X16" t="s">
-        <v>336</v>
+        <v>400</v>
       </c>
       <c r="Y16">
         <v>2.4397500000000001</v>
@@ -8761,15 +9636,48 @@
         <v>0.2073283908163579</v>
       </c>
     </row>
-    <row r="17" spans="15:26">
+    <row r="17" spans="2:26">
+      <c r="B17" t="s">
+        <v>172</v>
+      </c>
+      <c r="C17" t="s">
+        <v>414</v>
+      </c>
+      <c r="D17" t="s">
+        <v>415</v>
+      </c>
+      <c r="E17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" t="s">
+        <v>21</v>
+      </c>
+      <c r="G17" t="s">
+        <v>175</v>
+      </c>
+      <c r="H17" t="s">
+        <v>176</v>
+      </c>
+      <c r="J17" t="s">
+        <v>414</v>
+      </c>
+      <c r="K17" t="s">
+        <v>349</v>
+      </c>
+      <c r="L17">
+        <v>0.79119197542061592</v>
+      </c>
+      <c r="M17">
+        <v>8.8058478981552502E-2</v>
+      </c>
       <c r="O17" t="s">
         <v>172</v>
       </c>
       <c r="P17" t="s">
-        <v>363</v>
+        <v>434</v>
       </c>
       <c r="Q17" t="s">
-        <v>364</v>
+        <v>435</v>
       </c>
       <c r="R17" t="s">
         <v>10</v>
@@ -8784,10 +9692,10 @@
         <v>176</v>
       </c>
       <c r="W17" t="s">
-        <v>363</v>
+        <v>434</v>
       </c>
       <c r="X17" t="s">
-        <v>337</v>
+        <v>386</v>
       </c>
       <c r="Y17">
         <v>0.189</v>
@@ -8796,15 +9704,48 @@
         <v>0.2270784544752667</v>
       </c>
     </row>
-    <row r="18" spans="15:26">
+    <row r="18" spans="2:26">
+      <c r="B18" t="s">
+        <v>172</v>
+      </c>
+      <c r="C18" t="s">
+        <v>416</v>
+      </c>
+      <c r="D18" t="s">
+        <v>417</v>
+      </c>
+      <c r="E18" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" t="s">
+        <v>21</v>
+      </c>
+      <c r="G18" t="s">
+        <v>175</v>
+      </c>
+      <c r="H18" t="s">
+        <v>176</v>
+      </c>
+      <c r="J18" t="s">
+        <v>416</v>
+      </c>
+      <c r="K18" t="s">
+        <v>355</v>
+      </c>
+      <c r="L18">
+        <v>0.24323366751388889</v>
+      </c>
+      <c r="M18">
+        <v>0.1202939608755122</v>
+      </c>
       <c r="O18" t="s">
         <v>172</v>
       </c>
       <c r="P18" t="s">
-        <v>365</v>
+        <v>436</v>
       </c>
       <c r="Q18" t="s">
-        <v>366</v>
+        <v>437</v>
       </c>
       <c r="R18" t="s">
         <v>10</v>
@@ -8819,10 +9760,10 @@
         <v>176</v>
       </c>
       <c r="W18" t="s">
-        <v>365</v>
+        <v>436</v>
       </c>
       <c r="X18" t="s">
-        <v>334</v>
+        <v>398</v>
       </c>
       <c r="Y18">
         <v>5.9077500000000001</v>
@@ -8831,15 +9772,48 @@
         <v>0.30290113719049688</v>
       </c>
     </row>
-    <row r="19" spans="15:26">
+    <row r="19" spans="2:26">
+      <c r="B19" t="s">
+        <v>172</v>
+      </c>
+      <c r="C19" t="s">
+        <v>418</v>
+      </c>
+      <c r="D19" t="s">
+        <v>419</v>
+      </c>
+      <c r="E19" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19" t="s">
+        <v>21</v>
+      </c>
+      <c r="G19" t="s">
+        <v>175</v>
+      </c>
+      <c r="H19" t="s">
+        <v>176</v>
+      </c>
+      <c r="J19" t="s">
+        <v>418</v>
+      </c>
+      <c r="K19" t="s">
+        <v>363</v>
+      </c>
+      <c r="L19">
+        <v>0.17228445655487193</v>
+      </c>
+      <c r="M19">
+        <v>0.13546859013825549</v>
+      </c>
       <c r="O19" t="s">
         <v>172</v>
       </c>
       <c r="P19" t="s">
-        <v>367</v>
+        <v>438</v>
       </c>
       <c r="Q19" t="s">
-        <v>368</v>
+        <v>439</v>
       </c>
       <c r="R19" t="s">
         <v>10</v>
@@ -8854,10 +9828,10 @@
         <v>176</v>
       </c>
       <c r="W19" t="s">
-        <v>367</v>
+        <v>438</v>
       </c>
       <c r="X19" t="s">
-        <v>323</v>
+        <v>401</v>
       </c>
       <c r="Y19">
         <v>3.9195000000000002</v>
@@ -8866,15 +9840,48 @@
         <v>0.26737027878599101</v>
       </c>
     </row>
-    <row r="20" spans="15:26">
+    <row r="20" spans="2:26">
+      <c r="B20" t="s">
+        <v>172</v>
+      </c>
+      <c r="C20" t="s">
+        <v>420</v>
+      </c>
+      <c r="D20" t="s">
+        <v>421</v>
+      </c>
+      <c r="E20" t="s">
+        <v>10</v>
+      </c>
+      <c r="F20" t="s">
+        <v>21</v>
+      </c>
+      <c r="G20" t="s">
+        <v>175</v>
+      </c>
+      <c r="H20" t="s">
+        <v>176</v>
+      </c>
+      <c r="J20" t="s">
+        <v>420</v>
+      </c>
+      <c r="K20" t="s">
+        <v>353</v>
+      </c>
+      <c r="L20">
+        <v>0.42007398105454308</v>
+      </c>
+      <c r="M20">
+        <v>0.1245870774956743</v>
+      </c>
       <c r="O20" t="s">
         <v>172</v>
       </c>
       <c r="P20" t="s">
-        <v>369</v>
+        <v>440</v>
       </c>
       <c r="Q20" t="s">
-        <v>370</v>
+        <v>441</v>
       </c>
       <c r="R20" t="s">
         <v>10</v>
@@ -8889,10 +9896,10 @@
         <v>176</v>
       </c>
       <c r="W20" t="s">
-        <v>369</v>
+        <v>440</v>
       </c>
       <c r="X20" t="s">
-        <v>331</v>
+        <v>392</v>
       </c>
       <c r="Y20">
         <v>7.3425000000000002</v>
@@ -8907,13 +9914,13 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85642FD6-D606-4145-B5AC-EFA2DFDEDB0B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F496994-AA89-4BCA-9207-7F75FFFBA2A5}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="9" spans="2:16">
       <c r="B9" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="J9" t="s">
         <v>164</v>
@@ -8924,10 +9931,10 @@
         <v>166</v>
       </c>
       <c r="C10" t="s">
-        <v>268</v>
+        <v>303</v>
       </c>
       <c r="D10" t="s">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="E10">
         <v>2023</v>
@@ -8965,7 +9972,7 @@
     </row>
     <row r="11" spans="2:16">
       <c r="B11" t="s">
-        <v>371</v>
+        <v>442</v>
       </c>
       <c r="C11" t="s">
         <v>31</v>
@@ -8989,7 +9996,7 @@
         <v>172</v>
       </c>
       <c r="K11" t="s">
-        <v>371</v>
+        <v>442</v>
       </c>
       <c r="M11" t="s">
         <v>10</v>
@@ -8998,15 +10005,15 @@
         <v>21</v>
       </c>
       <c r="O11" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="P11" t="s">
-        <v>393</v>
+        <v>464</v>
       </c>
     </row>
     <row r="12" spans="2:16">
       <c r="B12" t="s">
-        <v>371</v>
+        <v>442</v>
       </c>
       <c r="C12" t="s">
         <v>31</v>
@@ -9024,13 +10031,13 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="H12" t="s">
-        <v>372</v>
+        <v>443</v>
       </c>
       <c r="J12" t="s">
         <v>172</v>
       </c>
       <c r="K12" t="s">
-        <v>376</v>
+        <v>447</v>
       </c>
       <c r="M12" t="s">
         <v>10</v>
@@ -9039,15 +10046,15 @@
         <v>21</v>
       </c>
       <c r="O12" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="P12" t="s">
-        <v>393</v>
+        <v>464</v>
       </c>
     </row>
     <row r="13" spans="2:16">
       <c r="B13" t="s">
-        <v>371</v>
+        <v>442</v>
       </c>
       <c r="C13" t="s">
         <v>31</v>
@@ -9065,13 +10072,13 @@
         <v>4200</v>
       </c>
       <c r="H13" t="s">
-        <v>373</v>
+        <v>444</v>
       </c>
       <c r="J13" t="s">
         <v>172</v>
       </c>
       <c r="K13" t="s">
-        <v>377</v>
+        <v>448</v>
       </c>
       <c r="M13" t="s">
         <v>10</v>
@@ -9080,15 +10087,15 @@
         <v>21</v>
       </c>
       <c r="O13" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="P13" t="s">
-        <v>393</v>
+        <v>464</v>
       </c>
     </row>
     <row r="14" spans="2:16">
       <c r="B14" t="s">
-        <v>371</v>
+        <v>442</v>
       </c>
       <c r="C14" t="s">
         <v>31</v>
@@ -9106,13 +10113,13 @@
         <v>145</v>
       </c>
       <c r="H14" t="s">
-        <v>374</v>
+        <v>445</v>
       </c>
       <c r="J14" t="s">
         <v>172</v>
       </c>
       <c r="K14" t="s">
-        <v>378</v>
+        <v>449</v>
       </c>
       <c r="M14" t="s">
         <v>10</v>
@@ -9121,15 +10128,15 @@
         <v>21</v>
       </c>
       <c r="O14" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="P14" t="s">
-        <v>393</v>
+        <v>464</v>
       </c>
     </row>
     <row r="15" spans="2:16">
       <c r="B15" t="s">
-        <v>371</v>
+        <v>442</v>
       </c>
       <c r="C15" t="s">
         <v>31</v>
@@ -9147,13 +10154,13 @@
         <v>3</v>
       </c>
       <c r="H15" t="s">
-        <v>375</v>
+        <v>446</v>
       </c>
       <c r="J15" t="s">
         <v>172</v>
       </c>
       <c r="K15" t="s">
-        <v>379</v>
+        <v>450</v>
       </c>
       <c r="M15" t="s">
         <v>10</v>
@@ -9162,15 +10169,15 @@
         <v>21</v>
       </c>
       <c r="O15" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="P15" t="s">
-        <v>393</v>
+        <v>464</v>
       </c>
     </row>
     <row r="16" spans="2:16">
       <c r="B16" t="s">
-        <v>376</v>
+        <v>447</v>
       </c>
       <c r="C16" t="s">
         <v>31</v>
@@ -9194,7 +10201,7 @@
         <v>172</v>
       </c>
       <c r="K16" t="s">
-        <v>380</v>
+        <v>451</v>
       </c>
       <c r="M16" t="s">
         <v>10</v>
@@ -9203,15 +10210,15 @@
         <v>21</v>
       </c>
       <c r="O16" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="P16" t="s">
-        <v>393</v>
+        <v>464</v>
       </c>
     </row>
     <row r="17" spans="2:16">
       <c r="B17" t="s">
-        <v>376</v>
+        <v>447</v>
       </c>
       <c r="C17" t="s">
         <v>31</v>
@@ -9229,13 +10236,13 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="H17" t="s">
-        <v>372</v>
+        <v>443</v>
       </c>
       <c r="J17" t="s">
         <v>172</v>
       </c>
       <c r="K17" t="s">
-        <v>381</v>
+        <v>452</v>
       </c>
       <c r="M17" t="s">
         <v>10</v>
@@ -9244,15 +10251,15 @@
         <v>21</v>
       </c>
       <c r="O17" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="P17" t="s">
-        <v>393</v>
+        <v>464</v>
       </c>
     </row>
     <row r="18" spans="2:16">
       <c r="B18" t="s">
-        <v>376</v>
+        <v>447</v>
       </c>
       <c r="C18" t="s">
         <v>31</v>
@@ -9270,13 +10277,13 @@
         <v>2050</v>
       </c>
       <c r="H18" t="s">
-        <v>373</v>
+        <v>444</v>
       </c>
       <c r="J18" t="s">
         <v>172</v>
       </c>
       <c r="K18" t="s">
-        <v>382</v>
+        <v>453</v>
       </c>
       <c r="M18" t="s">
         <v>10</v>
@@ -9285,15 +10292,15 @@
         <v>21</v>
       </c>
       <c r="O18" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="P18" t="s">
-        <v>393</v>
+        <v>464</v>
       </c>
     </row>
     <row r="19" spans="2:16">
       <c r="B19" t="s">
-        <v>376</v>
+        <v>447</v>
       </c>
       <c r="C19" t="s">
         <v>31</v>
@@ -9311,13 +10318,13 @@
         <v>70</v>
       </c>
       <c r="H19" t="s">
-        <v>374</v>
+        <v>445</v>
       </c>
       <c r="J19" t="s">
         <v>172</v>
       </c>
       <c r="K19" t="s">
-        <v>383</v>
+        <v>454</v>
       </c>
       <c r="M19" t="s">
         <v>10</v>
@@ -9326,15 +10333,15 @@
         <v>21</v>
       </c>
       <c r="O19" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="P19" t="s">
-        <v>393</v>
+        <v>464</v>
       </c>
     </row>
     <row r="20" spans="2:16">
       <c r="B20" t="s">
-        <v>376</v>
+        <v>447</v>
       </c>
       <c r="C20" t="s">
         <v>31</v>
@@ -9352,13 +10359,13 @@
         <v>3</v>
       </c>
       <c r="H20" t="s">
-        <v>375</v>
+        <v>446</v>
       </c>
       <c r="J20" t="s">
         <v>172</v>
       </c>
       <c r="K20" t="s">
-        <v>384</v>
+        <v>455</v>
       </c>
       <c r="M20" t="s">
         <v>10</v>
@@ -9367,15 +10374,15 @@
         <v>21</v>
       </c>
       <c r="O20" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="P20" t="s">
-        <v>393</v>
+        <v>464</v>
       </c>
     </row>
     <row r="21" spans="2:16">
       <c r="B21" t="s">
-        <v>377</v>
+        <v>448</v>
       </c>
       <c r="C21" t="s">
         <v>33</v>
@@ -9399,7 +10406,7 @@
         <v>172</v>
       </c>
       <c r="K21" t="s">
-        <v>385</v>
+        <v>456</v>
       </c>
       <c r="M21" t="s">
         <v>10</v>
@@ -9408,15 +10415,15 @@
         <v>21</v>
       </c>
       <c r="O21" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="P21" t="s">
-        <v>393</v>
+        <v>464</v>
       </c>
     </row>
     <row r="22" spans="2:16">
       <c r="B22" t="s">
-        <v>377</v>
+        <v>448</v>
       </c>
       <c r="C22" t="s">
         <v>33</v>
@@ -9434,13 +10441,13 @@
         <v>700</v>
       </c>
       <c r="H22" t="s">
-        <v>373</v>
+        <v>444</v>
       </c>
       <c r="J22" t="s">
         <v>172</v>
       </c>
       <c r="K22" t="s">
-        <v>386</v>
+        <v>457</v>
       </c>
       <c r="M22" t="s">
         <v>10</v>
@@ -9449,15 +10456,15 @@
         <v>21</v>
       </c>
       <c r="O22" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="P22" t="s">
-        <v>393</v>
+        <v>464</v>
       </c>
     </row>
     <row r="23" spans="2:16">
       <c r="B23" t="s">
-        <v>377</v>
+        <v>448</v>
       </c>
       <c r="C23" t="s">
         <v>33</v>
@@ -9475,13 +10482,13 @@
         <v>25</v>
       </c>
       <c r="H23" t="s">
-        <v>374</v>
+        <v>445</v>
       </c>
       <c r="J23" t="s">
         <v>172</v>
       </c>
       <c r="K23" t="s">
-        <v>387</v>
+        <v>458</v>
       </c>
       <c r="M23" t="s">
         <v>10</v>
@@ -9490,15 +10497,15 @@
         <v>21</v>
       </c>
       <c r="O23" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="P23" t="s">
-        <v>393</v>
+        <v>464</v>
       </c>
     </row>
     <row r="24" spans="2:16">
       <c r="B24" t="s">
-        <v>378</v>
+        <v>449</v>
       </c>
       <c r="C24" t="s">
         <v>33</v>
@@ -9522,7 +10529,7 @@
         <v>172</v>
       </c>
       <c r="K24" t="s">
-        <v>388</v>
+        <v>459</v>
       </c>
       <c r="M24" t="s">
         <v>10</v>
@@ -9531,15 +10538,15 @@
         <v>21</v>
       </c>
       <c r="O24" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="P24" t="s">
-        <v>393</v>
+        <v>464</v>
       </c>
     </row>
     <row r="25" spans="2:16">
       <c r="B25" t="s">
-        <v>378</v>
+        <v>449</v>
       </c>
       <c r="C25" t="s">
         <v>33</v>
@@ -9557,13 +10564,13 @@
         <v>1750</v>
       </c>
       <c r="H25" t="s">
-        <v>373</v>
+        <v>444</v>
       </c>
       <c r="J25" t="s">
         <v>172</v>
       </c>
       <c r="K25" t="s">
-        <v>389</v>
+        <v>460</v>
       </c>
       <c r="M25" t="s">
         <v>10</v>
@@ -9572,15 +10579,15 @@
         <v>21</v>
       </c>
       <c r="O25" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="P25" t="s">
-        <v>393</v>
+        <v>464</v>
       </c>
     </row>
     <row r="26" spans="2:16">
       <c r="B26" t="s">
-        <v>378</v>
+        <v>449</v>
       </c>
       <c r="C26" t="s">
         <v>33</v>
@@ -9598,13 +10605,13 @@
         <v>60</v>
       </c>
       <c r="H26" t="s">
-        <v>374</v>
+        <v>445</v>
       </c>
       <c r="J26" t="s">
         <v>172</v>
       </c>
       <c r="K26" t="s">
-        <v>390</v>
+        <v>461</v>
       </c>
       <c r="M26" t="s">
         <v>10</v>
@@ -9613,15 +10620,15 @@
         <v>21</v>
       </c>
       <c r="O26" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="P26" t="s">
-        <v>393</v>
+        <v>464</v>
       </c>
     </row>
     <row r="27" spans="2:16">
       <c r="B27" t="s">
-        <v>379</v>
+        <v>450</v>
       </c>
       <c r="C27" t="s">
         <v>32</v>
@@ -9645,7 +10652,7 @@
         <v>172</v>
       </c>
       <c r="K27" t="s">
-        <v>392</v>
+        <v>463</v>
       </c>
       <c r="M27" t="s">
         <v>10</v>
@@ -9654,15 +10661,15 @@
         <v>21</v>
       </c>
       <c r="O27" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="P27" t="s">
-        <v>393</v>
+        <v>464</v>
       </c>
     </row>
     <row r="28" spans="2:16">
       <c r="B28" t="s">
-        <v>379</v>
+        <v>450</v>
       </c>
       <c r="C28" t="s">
         <v>32</v>
@@ -9680,12 +10687,12 @@
         <v>3000</v>
       </c>
       <c r="H28" t="s">
-        <v>373</v>
+        <v>444</v>
       </c>
     </row>
     <row r="29" spans="2:16">
       <c r="B29" t="s">
-        <v>379</v>
+        <v>450</v>
       </c>
       <c r="C29" t="s">
         <v>32</v>
@@ -9703,12 +10710,12 @@
         <v>120</v>
       </c>
       <c r="H29" t="s">
-        <v>374</v>
+        <v>445</v>
       </c>
     </row>
     <row r="30" spans="2:16">
       <c r="B30" t="s">
-        <v>380</v>
+        <v>451</v>
       </c>
       <c r="C30" t="s">
         <v>33</v>
@@ -9731,7 +10738,7 @@
     </row>
     <row r="31" spans="2:16">
       <c r="B31" t="s">
-        <v>380</v>
+        <v>451</v>
       </c>
       <c r="C31" t="s">
         <v>33</v>
@@ -9749,12 +10756,12 @@
         <v>400</v>
       </c>
       <c r="H31" t="s">
-        <v>373</v>
+        <v>444</v>
       </c>
     </row>
     <row r="32" spans="2:16">
       <c r="B32" t="s">
-        <v>380</v>
+        <v>451</v>
       </c>
       <c r="C32" t="s">
         <v>33</v>
@@ -9772,12 +10779,12 @@
         <v>20</v>
       </c>
       <c r="H32" t="s">
-        <v>374</v>
+        <v>445</v>
       </c>
     </row>
     <row r="33" spans="2:8">
       <c r="B33" t="s">
-        <v>381</v>
+        <v>452</v>
       </c>
       <c r="C33" t="s">
         <v>28</v>
@@ -9800,7 +10807,7 @@
     </row>
     <row r="34" spans="2:8">
       <c r="B34" t="s">
-        <v>381</v>
+        <v>452</v>
       </c>
       <c r="C34" t="s">
         <v>28</v>
@@ -9818,12 +10825,12 @@
         <v>0.4</v>
       </c>
       <c r="H34" t="s">
-        <v>372</v>
+        <v>443</v>
       </c>
     </row>
     <row r="35" spans="2:8">
       <c r="B35" t="s">
-        <v>381</v>
+        <v>452</v>
       </c>
       <c r="C35" t="s">
         <v>28</v>
@@ -9841,12 +10848,12 @@
         <v>2000</v>
       </c>
       <c r="H35" t="s">
-        <v>373</v>
+        <v>444</v>
       </c>
     </row>
     <row r="36" spans="2:8">
       <c r="B36" t="s">
-        <v>381</v>
+        <v>452</v>
       </c>
       <c r="C36" t="s">
         <v>28</v>
@@ -9864,12 +10871,12 @@
         <v>50</v>
       </c>
       <c r="H36" t="s">
-        <v>374</v>
+        <v>445</v>
       </c>
     </row>
     <row r="37" spans="2:8">
       <c r="B37" t="s">
-        <v>381</v>
+        <v>452</v>
       </c>
       <c r="C37" t="s">
         <v>28</v>
@@ -9887,12 +10894,12 @@
         <v>4</v>
       </c>
       <c r="H37" t="s">
-        <v>375</v>
+        <v>446</v>
       </c>
     </row>
     <row r="38" spans="2:8">
       <c r="B38" t="s">
-        <v>382</v>
+        <v>453</v>
       </c>
       <c r="C38" t="s">
         <v>33</v>
@@ -9915,7 +10922,7 @@
     </row>
     <row r="39" spans="2:8">
       <c r="B39" t="s">
-        <v>382</v>
+        <v>453</v>
       </c>
       <c r="C39" t="s">
         <v>33</v>
@@ -9933,12 +10940,12 @@
         <v>1500</v>
       </c>
       <c r="H39" t="s">
-        <v>373</v>
+        <v>444</v>
       </c>
     </row>
     <row r="40" spans="2:8">
       <c r="B40" t="s">
-        <v>382</v>
+        <v>453</v>
       </c>
       <c r="C40" t="s">
         <v>33</v>
@@ -9956,12 +10963,12 @@
         <v>70</v>
       </c>
       <c r="H40" t="s">
-        <v>374</v>
+        <v>445</v>
       </c>
     </row>
     <row r="41" spans="2:8">
       <c r="B41" t="s">
-        <v>383</v>
+        <v>454</v>
       </c>
       <c r="C41" t="s">
         <v>32</v>
@@ -9984,7 +10991,7 @@
     </row>
     <row r="42" spans="2:8">
       <c r="B42" t="s">
-        <v>383</v>
+        <v>454</v>
       </c>
       <c r="C42" t="s">
         <v>32</v>
@@ -10002,12 +11009,12 @@
         <v>3550</v>
       </c>
       <c r="H42" t="s">
-        <v>373</v>
+        <v>444</v>
       </c>
     </row>
     <row r="43" spans="2:8">
       <c r="B43" t="s">
-        <v>383</v>
+        <v>454</v>
       </c>
       <c r="C43" t="s">
         <v>32</v>
@@ -10025,12 +11032,12 @@
         <v>170</v>
       </c>
       <c r="H43" t="s">
-        <v>374</v>
+        <v>445</v>
       </c>
     </row>
     <row r="44" spans="2:8">
       <c r="B44" t="s">
-        <v>384</v>
+        <v>455</v>
       </c>
       <c r="C44" t="s">
         <v>36</v>
@@ -10053,7 +11060,7 @@
     </row>
     <row r="45" spans="2:8">
       <c r="B45" t="s">
-        <v>384</v>
+        <v>455</v>
       </c>
       <c r="C45" t="s">
         <v>36</v>
@@ -10071,12 +11078,12 @@
         <v>2800</v>
       </c>
       <c r="H45" t="s">
-        <v>373</v>
+        <v>444</v>
       </c>
     </row>
     <row r="46" spans="2:8">
       <c r="B46" t="s">
-        <v>384</v>
+        <v>455</v>
       </c>
       <c r="C46" t="s">
         <v>36</v>
@@ -10094,12 +11101,12 @@
         <v>140</v>
       </c>
       <c r="H46" t="s">
-        <v>374</v>
+        <v>445</v>
       </c>
     </row>
     <row r="47" spans="2:8">
       <c r="B47" t="s">
-        <v>385</v>
+        <v>456</v>
       </c>
       <c r="C47" t="s">
         <v>32</v>
@@ -10122,7 +11129,7 @@
     </row>
     <row r="48" spans="2:8">
       <c r="B48" t="s">
-        <v>385</v>
+        <v>456</v>
       </c>
       <c r="C48" t="s">
         <v>32</v>
@@ -10140,12 +11147,12 @@
         <v>3650</v>
       </c>
       <c r="H48" t="s">
-        <v>373</v>
+        <v>444</v>
       </c>
     </row>
     <row r="49" spans="2:8">
       <c r="B49" t="s">
-        <v>385</v>
+        <v>456</v>
       </c>
       <c r="C49" t="s">
         <v>32</v>
@@ -10163,12 +11170,12 @@
         <v>145</v>
       </c>
       <c r="H49" t="s">
-        <v>374</v>
+        <v>445</v>
       </c>
     </row>
     <row r="50" spans="2:8">
       <c r="B50" t="s">
-        <v>386</v>
+        <v>457</v>
       </c>
       <c r="C50" t="s">
         <v>27</v>
@@ -10191,7 +11198,7 @@
     </row>
     <row r="51" spans="2:8">
       <c r="B51" t="s">
-        <v>386</v>
+        <v>457</v>
       </c>
       <c r="C51" t="s">
         <v>27</v>
@@ -10209,12 +11216,12 @@
         <v>0.22</v>
       </c>
       <c r="H51" t="s">
-        <v>372</v>
+        <v>443</v>
       </c>
     </row>
     <row r="52" spans="2:8">
       <c r="B52" t="s">
-        <v>386</v>
+        <v>457</v>
       </c>
       <c r="C52" t="s">
         <v>27</v>
@@ -10232,12 +11239,12 @@
         <v>300</v>
       </c>
       <c r="H52" t="s">
-        <v>373</v>
+        <v>444</v>
       </c>
     </row>
     <row r="53" spans="2:8">
       <c r="B53" t="s">
-        <v>386</v>
+        <v>457</v>
       </c>
       <c r="C53" t="s">
         <v>27</v>
@@ -10255,12 +11262,12 @@
         <v>10</v>
       </c>
       <c r="H53" t="s">
-        <v>374</v>
+        <v>445</v>
       </c>
     </row>
     <row r="54" spans="2:8">
       <c r="B54" t="s">
-        <v>386</v>
+        <v>457</v>
       </c>
       <c r="C54" t="s">
         <v>27</v>
@@ -10278,12 +11285,12 @@
         <v>1.5</v>
       </c>
       <c r="H54" t="s">
-        <v>375</v>
+        <v>446</v>
       </c>
     </row>
     <row r="55" spans="2:8">
       <c r="B55" t="s">
-        <v>387</v>
+        <v>458</v>
       </c>
       <c r="C55" t="s">
         <v>32</v>
@@ -10306,7 +11313,7 @@
     </row>
     <row r="56" spans="2:8">
       <c r="B56" t="s">
-        <v>387</v>
+        <v>458</v>
       </c>
       <c r="C56" t="s">
         <v>32</v>
@@ -10324,12 +11331,12 @@
         <v>1000</v>
       </c>
       <c r="H56" t="s">
-        <v>373</v>
+        <v>444</v>
       </c>
     </row>
     <row r="57" spans="2:8">
       <c r="B57" t="s">
-        <v>387</v>
+        <v>458</v>
       </c>
       <c r="C57" t="s">
         <v>32</v>
@@ -10347,12 +11354,12 @@
         <v>35</v>
       </c>
       <c r="H57" t="s">
-        <v>374</v>
+        <v>445</v>
       </c>
     </row>
     <row r="58" spans="2:8">
       <c r="B58" t="s">
-        <v>388</v>
+        <v>459</v>
       </c>
       <c r="C58" t="s">
         <v>32</v>
@@ -10375,7 +11382,7 @@
     </row>
     <row r="59" spans="2:8">
       <c r="B59" t="s">
-        <v>388</v>
+        <v>459</v>
       </c>
       <c r="C59" t="s">
         <v>32</v>
@@ -10393,12 +11400,12 @@
         <v>1200</v>
       </c>
       <c r="H59" t="s">
-        <v>373</v>
+        <v>444</v>
       </c>
     </row>
     <row r="60" spans="2:8">
       <c r="B60" t="s">
-        <v>388</v>
+        <v>459</v>
       </c>
       <c r="C60" t="s">
         <v>32</v>
@@ -10416,12 +11423,12 @@
         <v>50</v>
       </c>
       <c r="H60" t="s">
-        <v>374</v>
+        <v>445</v>
       </c>
     </row>
     <row r="61" spans="2:8">
       <c r="B61" t="s">
-        <v>389</v>
+        <v>460</v>
       </c>
       <c r="C61" t="s">
         <v>32</v>
@@ -10444,7 +11451,7 @@
     </row>
     <row r="62" spans="2:8">
       <c r="B62" t="s">
-        <v>389</v>
+        <v>460</v>
       </c>
       <c r="C62" t="s">
         <v>32</v>
@@ -10462,12 +11469,12 @@
         <v>1400</v>
       </c>
       <c r="H62" t="s">
-        <v>373</v>
+        <v>444</v>
       </c>
     </row>
     <row r="63" spans="2:8">
       <c r="B63" t="s">
-        <v>389</v>
+        <v>460</v>
       </c>
       <c r="C63" t="s">
         <v>32</v>
@@ -10485,15 +11492,15 @@
         <v>55</v>
       </c>
       <c r="H63" t="s">
-        <v>374</v>
+        <v>445</v>
       </c>
     </row>
     <row r="64" spans="2:8">
       <c r="B64" t="s">
-        <v>390</v>
+        <v>461</v>
       </c>
       <c r="C64" t="s">
-        <v>391</v>
+        <v>462</v>
       </c>
       <c r="D64" t="s">
         <v>19</v>
@@ -10513,10 +11520,10 @@
     </row>
     <row r="65" spans="2:8">
       <c r="B65" t="s">
-        <v>390</v>
+        <v>461</v>
       </c>
       <c r="C65" t="s">
-        <v>391</v>
+        <v>462</v>
       </c>
       <c r="D65" t="s">
         <v>19</v>
@@ -10531,15 +11538,15 @@
         <v>0.39</v>
       </c>
       <c r="H65" t="s">
-        <v>372</v>
+        <v>443</v>
       </c>
     </row>
     <row r="66" spans="2:8">
       <c r="B66" t="s">
-        <v>390</v>
+        <v>461</v>
       </c>
       <c r="C66" t="s">
-        <v>391</v>
+        <v>462</v>
       </c>
       <c r="D66" t="s">
         <v>19</v>
@@ -10554,15 +11561,15 @@
         <v>1360</v>
       </c>
       <c r="H66" t="s">
-        <v>373</v>
+        <v>444</v>
       </c>
     </row>
     <row r="67" spans="2:8">
       <c r="B67" t="s">
-        <v>390</v>
+        <v>461</v>
       </c>
       <c r="C67" t="s">
-        <v>391</v>
+        <v>462</v>
       </c>
       <c r="D67" t="s">
         <v>19</v>
@@ -10577,15 +11584,15 @@
         <v>40</v>
       </c>
       <c r="H67" t="s">
-        <v>374</v>
+        <v>445</v>
       </c>
     </row>
     <row r="68" spans="2:8">
       <c r="B68" t="s">
-        <v>390</v>
+        <v>461</v>
       </c>
       <c r="C68" t="s">
-        <v>391</v>
+        <v>462</v>
       </c>
       <c r="D68" t="s">
         <v>19</v>
@@ -10600,15 +11607,15 @@
         <v>3</v>
       </c>
       <c r="H68" t="s">
-        <v>375</v>
+        <v>446</v>
       </c>
     </row>
     <row r="69" spans="2:8">
       <c r="B69" t="s">
-        <v>392</v>
+        <v>463</v>
       </c>
       <c r="C69" t="s">
-        <v>391</v>
+        <v>462</v>
       </c>
       <c r="D69" t="s">
         <v>19</v>
@@ -10628,10 +11635,10 @@
     </row>
     <row r="70" spans="2:8">
       <c r="B70" t="s">
-        <v>392</v>
+        <v>463</v>
       </c>
       <c r="C70" t="s">
-        <v>391</v>
+        <v>462</v>
       </c>
       <c r="D70" t="s">
         <v>19</v>
@@ -10646,15 +11653,15 @@
         <v>0.3</v>
       </c>
       <c r="H70" t="s">
-        <v>372</v>
+        <v>443</v>
       </c>
     </row>
     <row r="71" spans="2:8">
       <c r="B71" t="s">
-        <v>392</v>
+        <v>463</v>
       </c>
       <c r="C71" t="s">
-        <v>391</v>
+        <v>462</v>
       </c>
       <c r="D71" t="s">
         <v>19</v>
@@ -10669,15 +11676,15 @@
         <v>1090</v>
       </c>
       <c r="H71" t="s">
-        <v>373</v>
+        <v>444</v>
       </c>
     </row>
     <row r="72" spans="2:8">
       <c r="B72" t="s">
-        <v>392</v>
+        <v>463</v>
       </c>
       <c r="C72" t="s">
-        <v>391</v>
+        <v>462</v>
       </c>
       <c r="D72" t="s">
         <v>19</v>
@@ -10692,15 +11699,15 @@
         <v>28</v>
       </c>
       <c r="H72" t="s">
-        <v>374</v>
+        <v>445</v>
       </c>
     </row>
     <row r="73" spans="2:8">
       <c r="B73" t="s">
-        <v>392</v>
+        <v>463</v>
       </c>
       <c r="C73" t="s">
-        <v>391</v>
+        <v>462</v>
       </c>
       <c r="D73" t="s">
         <v>19</v>
@@ -10715,7 +11722,7 @@
         <v>1.5</v>
       </c>
       <c r="H73" t="s">
-        <v>375</v>
+        <v>446</v>
       </c>
     </row>
   </sheetData>
@@ -10724,13 +11731,13 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E66F7586-3D6C-4951-9AB3-F0DF5F3738FD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2A57265-F5CC-4FFE-BBD6-1B69ECA38215}">
   <dimension ref="B2:M25"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="2" spans="2:13">
       <c r="B2" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="H2" t="s">
         <v>164</v>
@@ -10741,10 +11748,10 @@
         <v>166</v>
       </c>
       <c r="C3" t="s">
-        <v>268</v>
+        <v>303</v>
       </c>
       <c r="D3" t="s">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="E3" t="s">
         <v>146</v>
@@ -10759,10 +11766,10 @@
         <v>167</v>
       </c>
       <c r="K3" t="s">
-        <v>438</v>
+        <v>509</v>
       </c>
       <c r="L3" t="s">
-        <v>439</v>
+        <v>510</v>
       </c>
       <c r="M3" t="s">
         <v>170</v>
@@ -10770,25 +11777,25 @@
     </row>
     <row r="4" spans="2:13">
       <c r="B4" t="s">
-        <v>394</v>
+        <v>465</v>
       </c>
       <c r="C4" t="s">
-        <v>395</v>
+        <v>466</v>
       </c>
       <c r="D4" t="s">
-        <v>396</v>
+        <v>467</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="I4" t="s">
-        <v>394</v>
+        <v>465</v>
       </c>
       <c r="J4" t="s">
-        <v>440</v>
+        <v>511</v>
       </c>
       <c r="K4" t="s">
         <v>21</v>
@@ -10797,30 +11804,30 @@
         <v>10</v>
       </c>
       <c r="M4" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="5" spans="2:13">
       <c r="B5" t="s">
-        <v>397</v>
+        <v>468</v>
       </c>
       <c r="C5" t="s">
-        <v>396</v>
+        <v>467</v>
       </c>
       <c r="D5" t="s">
-        <v>395</v>
+        <v>466</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
       <c r="H5" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="I5" t="s">
-        <v>397</v>
+        <v>468</v>
       </c>
       <c r="J5" t="s">
-        <v>441</v>
+        <v>512</v>
       </c>
       <c r="K5" t="s">
         <v>21</v>
@@ -10829,30 +11836,30 @@
         <v>10</v>
       </c>
       <c r="M5" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="6" spans="2:13">
       <c r="B6" t="s">
-        <v>398</v>
+        <v>469</v>
       </c>
       <c r="C6" t="s">
-        <v>399</v>
+        <v>470</v>
       </c>
       <c r="D6" t="s">
-        <v>400</v>
+        <v>471</v>
       </c>
       <c r="E6">
         <v>1</v>
       </c>
       <c r="H6" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="I6" t="s">
-        <v>398</v>
+        <v>469</v>
       </c>
       <c r="J6" t="s">
-        <v>442</v>
+        <v>513</v>
       </c>
       <c r="K6" t="s">
         <v>21</v>
@@ -10861,30 +11868,30 @@
         <v>10</v>
       </c>
       <c r="M6" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="7" spans="2:13">
       <c r="B7" t="s">
-        <v>401</v>
+        <v>472</v>
       </c>
       <c r="C7" t="s">
-        <v>400</v>
+        <v>471</v>
       </c>
       <c r="D7" t="s">
-        <v>399</v>
+        <v>470</v>
       </c>
       <c r="E7">
         <v>1</v>
       </c>
       <c r="H7" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="I7" t="s">
-        <v>401</v>
+        <v>472</v>
       </c>
       <c r="J7" t="s">
-        <v>443</v>
+        <v>514</v>
       </c>
       <c r="K7" t="s">
         <v>21</v>
@@ -10893,30 +11900,30 @@
         <v>10</v>
       </c>
       <c r="M7" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="8" spans="2:13">
       <c r="B8" t="s">
-        <v>402</v>
+        <v>473</v>
       </c>
       <c r="C8" t="s">
-        <v>403</v>
+        <v>474</v>
       </c>
       <c r="D8" t="s">
-        <v>404</v>
+        <v>475</v>
       </c>
       <c r="E8">
         <v>1</v>
       </c>
       <c r="H8" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="I8" t="s">
-        <v>402</v>
+        <v>473</v>
       </c>
       <c r="J8" t="s">
-        <v>444</v>
+        <v>515</v>
       </c>
       <c r="K8" t="s">
         <v>21</v>
@@ -10925,30 +11932,30 @@
         <v>10</v>
       </c>
       <c r="M8" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="9" spans="2:13">
       <c r="B9" t="s">
-        <v>405</v>
+        <v>476</v>
       </c>
       <c r="C9" t="s">
-        <v>404</v>
+        <v>475</v>
       </c>
       <c r="D9" t="s">
-        <v>403</v>
+        <v>474</v>
       </c>
       <c r="E9">
         <v>1</v>
       </c>
       <c r="H9" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="I9" t="s">
-        <v>405</v>
+        <v>476</v>
       </c>
       <c r="J9" t="s">
-        <v>445</v>
+        <v>516</v>
       </c>
       <c r="K9" t="s">
         <v>21</v>
@@ -10957,30 +11964,30 @@
         <v>10</v>
       </c>
       <c r="M9" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="10" spans="2:13">
       <c r="B10" t="s">
-        <v>406</v>
+        <v>477</v>
       </c>
       <c r="C10" t="s">
-        <v>407</v>
+        <v>478</v>
       </c>
       <c r="D10" t="s">
-        <v>408</v>
+        <v>479</v>
       </c>
       <c r="E10">
         <v>1</v>
       </c>
       <c r="H10" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="I10" t="s">
-        <v>406</v>
+        <v>477</v>
       </c>
       <c r="J10" t="s">
-        <v>446</v>
+        <v>517</v>
       </c>
       <c r="K10" t="s">
         <v>21</v>
@@ -10989,30 +11996,30 @@
         <v>10</v>
       </c>
       <c r="M10" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11" spans="2:13">
       <c r="B11" t="s">
-        <v>409</v>
+        <v>480</v>
       </c>
       <c r="C11" t="s">
-        <v>408</v>
+        <v>479</v>
       </c>
       <c r="D11" t="s">
-        <v>407</v>
+        <v>478</v>
       </c>
       <c r="E11">
         <v>1</v>
       </c>
       <c r="H11" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="I11" t="s">
-        <v>409</v>
+        <v>480</v>
       </c>
       <c r="J11" t="s">
-        <v>447</v>
+        <v>518</v>
       </c>
       <c r="K11" t="s">
         <v>21</v>
@@ -11021,30 +12028,30 @@
         <v>10</v>
       </c>
       <c r="M11" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="12" spans="2:13">
       <c r="B12" t="s">
-        <v>410</v>
+        <v>481</v>
       </c>
       <c r="C12" t="s">
-        <v>411</v>
+        <v>482</v>
       </c>
       <c r="D12" t="s">
-        <v>412</v>
+        <v>483</v>
       </c>
       <c r="E12">
         <v>1</v>
       </c>
       <c r="H12" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="I12" t="s">
-        <v>410</v>
+        <v>481</v>
       </c>
       <c r="J12" t="s">
-        <v>448</v>
+        <v>519</v>
       </c>
       <c r="K12" t="s">
         <v>21</v>
@@ -11053,30 +12060,30 @@
         <v>10</v>
       </c>
       <c r="M12" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="13" spans="2:13">
       <c r="B13" t="s">
-        <v>413</v>
+        <v>484</v>
       </c>
       <c r="C13" t="s">
-        <v>412</v>
+        <v>483</v>
       </c>
       <c r="D13" t="s">
-        <v>411</v>
+        <v>482</v>
       </c>
       <c r="E13">
         <v>1</v>
       </c>
       <c r="H13" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="I13" t="s">
-        <v>413</v>
+        <v>484</v>
       </c>
       <c r="J13" t="s">
-        <v>449</v>
+        <v>520</v>
       </c>
       <c r="K13" t="s">
         <v>21</v>
@@ -11085,30 +12092,30 @@
         <v>10</v>
       </c>
       <c r="M13" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="14" spans="2:13">
       <c r="B14" t="s">
-        <v>414</v>
+        <v>485</v>
       </c>
       <c r="C14" t="s">
-        <v>415</v>
+        <v>486</v>
       </c>
       <c r="D14" t="s">
-        <v>416</v>
+        <v>487</v>
       </c>
       <c r="E14">
         <v>1</v>
       </c>
       <c r="H14" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="I14" t="s">
-        <v>414</v>
+        <v>485</v>
       </c>
       <c r="J14" t="s">
-        <v>450</v>
+        <v>521</v>
       </c>
       <c r="K14" t="s">
         <v>21</v>
@@ -11117,30 +12124,30 @@
         <v>10</v>
       </c>
       <c r="M14" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="15" spans="2:13">
       <c r="B15" t="s">
-        <v>417</v>
+        <v>488</v>
       </c>
       <c r="C15" t="s">
-        <v>416</v>
+        <v>487</v>
       </c>
       <c r="D15" t="s">
-        <v>415</v>
+        <v>486</v>
       </c>
       <c r="E15">
         <v>1</v>
       </c>
       <c r="H15" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="I15" t="s">
-        <v>417</v>
+        <v>488</v>
       </c>
       <c r="J15" t="s">
-        <v>451</v>
+        <v>522</v>
       </c>
       <c r="K15" t="s">
         <v>21</v>
@@ -11149,30 +12156,30 @@
         <v>10</v>
       </c>
       <c r="M15" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="16" spans="2:13">
       <c r="B16" t="s">
-        <v>418</v>
+        <v>489</v>
       </c>
       <c r="C16" t="s">
-        <v>419</v>
+        <v>490</v>
       </c>
       <c r="D16" t="s">
-        <v>420</v>
+        <v>491</v>
       </c>
       <c r="E16">
         <v>1</v>
       </c>
       <c r="H16" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="I16" t="s">
-        <v>418</v>
+        <v>489</v>
       </c>
       <c r="J16" t="s">
-        <v>452</v>
+        <v>523</v>
       </c>
       <c r="K16" t="s">
         <v>21</v>
@@ -11181,30 +12188,30 @@
         <v>10</v>
       </c>
       <c r="M16" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="17" spans="2:13">
       <c r="B17" t="s">
-        <v>421</v>
+        <v>492</v>
       </c>
       <c r="C17" t="s">
-        <v>420</v>
+        <v>491</v>
       </c>
       <c r="D17" t="s">
-        <v>419</v>
+        <v>490</v>
       </c>
       <c r="E17">
         <v>1</v>
       </c>
       <c r="H17" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="I17" t="s">
-        <v>421</v>
+        <v>492</v>
       </c>
       <c r="J17" t="s">
-        <v>453</v>
+        <v>524</v>
       </c>
       <c r="K17" t="s">
         <v>21</v>
@@ -11213,30 +12220,30 @@
         <v>10</v>
       </c>
       <c r="M17" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18" spans="2:13">
       <c r="B18" t="s">
-        <v>422</v>
+        <v>493</v>
       </c>
       <c r="C18" t="s">
-        <v>423</v>
+        <v>494</v>
       </c>
       <c r="D18" t="s">
-        <v>424</v>
+        <v>495</v>
       </c>
       <c r="E18">
         <v>1</v>
       </c>
       <c r="H18" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="I18" t="s">
-        <v>422</v>
+        <v>493</v>
       </c>
       <c r="J18" t="s">
-        <v>454</v>
+        <v>525</v>
       </c>
       <c r="K18" t="s">
         <v>21</v>
@@ -11245,30 +12252,30 @@
         <v>10</v>
       </c>
       <c r="M18" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="19" spans="2:13">
       <c r="B19" t="s">
-        <v>425</v>
+        <v>496</v>
       </c>
       <c r="C19" t="s">
-        <v>424</v>
+        <v>495</v>
       </c>
       <c r="D19" t="s">
-        <v>423</v>
+        <v>494</v>
       </c>
       <c r="E19">
         <v>1</v>
       </c>
       <c r="H19" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="I19" t="s">
-        <v>425</v>
+        <v>496</v>
       </c>
       <c r="J19" t="s">
-        <v>455</v>
+        <v>526</v>
       </c>
       <c r="K19" t="s">
         <v>21</v>
@@ -11277,30 +12284,30 @@
         <v>10</v>
       </c>
       <c r="M19" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="20" spans="2:13">
       <c r="B20" t="s">
-        <v>426</v>
+        <v>497</v>
       </c>
       <c r="C20" t="s">
-        <v>427</v>
+        <v>498</v>
       </c>
       <c r="D20" t="s">
-        <v>428</v>
+        <v>499</v>
       </c>
       <c r="E20">
         <v>1</v>
       </c>
       <c r="H20" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="I20" t="s">
-        <v>426</v>
+        <v>497</v>
       </c>
       <c r="J20" t="s">
-        <v>456</v>
+        <v>527</v>
       </c>
       <c r="K20" t="s">
         <v>21</v>
@@ -11309,30 +12316,30 @@
         <v>10</v>
       </c>
       <c r="M20" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="21" spans="2:13">
       <c r="B21" t="s">
-        <v>429</v>
+        <v>500</v>
       </c>
       <c r="C21" t="s">
-        <v>428</v>
+        <v>499</v>
       </c>
       <c r="D21" t="s">
-        <v>427</v>
+        <v>498</v>
       </c>
       <c r="E21">
         <v>1</v>
       </c>
       <c r="H21" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="I21" t="s">
-        <v>429</v>
+        <v>500</v>
       </c>
       <c r="J21" t="s">
-        <v>457</v>
+        <v>528</v>
       </c>
       <c r="K21" t="s">
         <v>21</v>
@@ -11341,30 +12348,30 @@
         <v>10</v>
       </c>
       <c r="M21" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="22" spans="2:13">
       <c r="B22" t="s">
-        <v>430</v>
+        <v>501</v>
       </c>
       <c r="C22" t="s">
-        <v>431</v>
+        <v>502</v>
       </c>
       <c r="D22" t="s">
-        <v>432</v>
+        <v>503</v>
       </c>
       <c r="E22">
         <v>1</v>
       </c>
       <c r="H22" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="I22" t="s">
-        <v>430</v>
+        <v>501</v>
       </c>
       <c r="J22" t="s">
-        <v>458</v>
+        <v>529</v>
       </c>
       <c r="K22" t="s">
         <v>21</v>
@@ -11373,30 +12380,30 @@
         <v>10</v>
       </c>
       <c r="M22" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="23" spans="2:13">
       <c r="B23" t="s">
-        <v>433</v>
+        <v>504</v>
       </c>
       <c r="C23" t="s">
-        <v>432</v>
+        <v>503</v>
       </c>
       <c r="D23" t="s">
-        <v>431</v>
+        <v>502</v>
       </c>
       <c r="E23">
         <v>1</v>
       </c>
       <c r="H23" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="I23" t="s">
-        <v>433</v>
+        <v>504</v>
       </c>
       <c r="J23" t="s">
-        <v>459</v>
+        <v>530</v>
       </c>
       <c r="K23" t="s">
         <v>21</v>
@@ -11405,30 +12412,30 @@
         <v>10</v>
       </c>
       <c r="M23" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="24" spans="2:13">
       <c r="B24" t="s">
-        <v>434</v>
+        <v>505</v>
       </c>
       <c r="C24" t="s">
-        <v>435</v>
+        <v>506</v>
       </c>
       <c r="D24" t="s">
-        <v>436</v>
+        <v>507</v>
       </c>
       <c r="E24">
         <v>1</v>
       </c>
       <c r="H24" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="I24" t="s">
-        <v>434</v>
+        <v>505</v>
       </c>
       <c r="J24" t="s">
-        <v>460</v>
+        <v>531</v>
       </c>
       <c r="K24" t="s">
         <v>21</v>
@@ -11437,30 +12444,30 @@
         <v>10</v>
       </c>
       <c r="M24" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="25" spans="2:13">
       <c r="B25" t="s">
-        <v>437</v>
+        <v>508</v>
       </c>
       <c r="C25" t="s">
-        <v>436</v>
+        <v>507</v>
       </c>
       <c r="D25" t="s">
-        <v>435</v>
+        <v>506</v>
       </c>
       <c r="E25">
         <v>1</v>
       </c>
       <c r="H25" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="I25" t="s">
-        <v>437</v>
+        <v>508</v>
       </c>
       <c r="J25" t="s">
-        <v>461</v>
+        <v>532</v>
       </c>
       <c r="K25" t="s">
         <v>21</v>
@@ -11469,7 +12476,7 @@
         <v>10</v>
       </c>
       <c r="M25" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
   </sheetData>
